--- a/Human-JAVA/Human-1110_mini_project/1108JavaTASK.xlsx
+++ b/Human-JAVA/Human-1110_mini_project/1108JavaTASK.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuuri/Study/Human-JAVA/Human-1110_mini_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8906F8-A478-DE4F-94FC-7D2374933F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F92049-F565-A943-9D3A-6F1352D02A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15420" yWindow="500" windowWidth="25540" windowHeight="22540" activeTab="4" xr2:uid="{DE03512C-061F-BB44-8A5D-89689A53AA28}"/>
+    <workbookView xWindow="54560" yWindow="320" windowWidth="25540" windowHeight="21580" activeTab="1" xr2:uid="{DE03512C-061F-BB44-8A5D-89689A53AA28}"/>
   </bookViews>
   <sheets>
     <sheet name="명세서" sheetId="1" r:id="rId1"/>
     <sheet name="패키지_클래스설명" sheetId="6" r:id="rId2"/>
-    <sheet name="시나리오" sheetId="5" r:id="rId3"/>
-    <sheet name="Default Qurey" sheetId="2" r:id="rId4"/>
+    <sheet name="Default Qurey" sheetId="2" r:id="rId3"/>
+    <sheet name="시나리오" sheetId="5" r:id="rId4"/>
     <sheet name="Test Qurey" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
@@ -13365,7 +13365,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -13483,76 +13483,19 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -13573,59 +13516,62 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -14007,669 +13953,669 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="37">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46" t="s">
+      <c r="C3" s="60"/>
+      <c r="D3" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45" t="s">
+      <c r="C4" s="58"/>
+      <c r="D4" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="45"/>
+      <c r="E4" s="58"/>
       <c r="F4" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="45" t="s">
+      <c r="G4" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="45"/>
+      <c r="H4" s="58"/>
       <c r="I4" s="16"/>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45" t="s">
+      <c r="C5" s="58"/>
+      <c r="D5" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="45"/>
+      <c r="E5" s="58"/>
       <c r="F5" s="16"/>
-      <c r="G5" s="45" t="s">
+      <c r="G5" s="58" t="s">
         <v>267</v>
       </c>
-      <c r="H5" s="45"/>
+      <c r="H5" s="58"/>
       <c r="I5" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45" t="s">
+      <c r="C6" s="58"/>
+      <c r="D6" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="45"/>
+      <c r="E6" s="58"/>
       <c r="F6" s="16"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
       <c r="I6" s="16" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45" t="s">
+      <c r="C7" s="58"/>
+      <c r="D7" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="45"/>
+      <c r="E7" s="58"/>
       <c r="F7" s="16"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
       <c r="I7" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45" t="s">
+      <c r="C8" s="58"/>
+      <c r="D8" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="45"/>
+      <c r="E8" s="58"/>
       <c r="F8" s="16"/>
-      <c r="G8" s="45" t="s">
+      <c r="G8" s="58" t="s">
         <v>272</v>
       </c>
-      <c r="H8" s="45"/>
+      <c r="H8" s="58"/>
       <c r="I8" s="16" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
       <c r="F9" s="16"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
       <c r="I9" s="16"/>
     </row>
     <row r="11" spans="2:9">
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46" t="s">
+      <c r="C11" s="60"/>
+      <c r="D11" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
       <c r="I11" s="15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="2:9">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45" t="s">
+      <c r="C12" s="58"/>
+      <c r="D12" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="45"/>
+      <c r="E12" s="58"/>
       <c r="F12" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="45" t="s">
+      <c r="G12" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="45"/>
+      <c r="H12" s="58"/>
       <c r="I12" s="16"/>
     </row>
     <row r="13" spans="2:9">
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45" t="s">
+      <c r="C13" s="58"/>
+      <c r="D13" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="45"/>
+      <c r="E13" s="58"/>
       <c r="F13" s="16"/>
-      <c r="G13" s="45" t="s">
+      <c r="G13" s="58" t="s">
         <v>267</v>
       </c>
-      <c r="H13" s="45"/>
+      <c r="H13" s="58"/>
       <c r="I13" s="16" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="2:9">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45" t="s">
+      <c r="C14" s="58"/>
+      <c r="D14" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="45"/>
+      <c r="E14" s="58"/>
       <c r="F14" s="16"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="16" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="15" spans="2:9">
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45" t="s">
+      <c r="C15" s="58"/>
+      <c r="D15" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="45"/>
+      <c r="E15" s="58"/>
       <c r="F15" s="16"/>
-      <c r="G15" s="45" t="s">
+      <c r="G15" s="58" t="s">
         <v>272</v>
       </c>
-      <c r="H15" s="45"/>
+      <c r="H15" s="58"/>
       <c r="I15" s="16" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46" t="s">
+      <c r="C17" s="60"/>
+      <c r="D17" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45" t="s">
+      <c r="C18" s="58"/>
+      <c r="D18" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="45"/>
+      <c r="E18" s="58"/>
       <c r="F18" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="45" t="s">
+      <c r="G18" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="45"/>
+      <c r="H18" s="58"/>
       <c r="I18" s="16"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45" t="s">
+      <c r="C19" s="58"/>
+      <c r="D19" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="45"/>
+      <c r="E19" s="58"/>
       <c r="F19" s="16"/>
-      <c r="G19" s="45" t="s">
+      <c r="G19" s="58" t="s">
         <v>267</v>
       </c>
-      <c r="H19" s="45"/>
+      <c r="H19" s="58"/>
       <c r="I19" s="16" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45" t="s">
+      <c r="C20" s="58"/>
+      <c r="D20" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="45"/>
+      <c r="E20" s="58"/>
       <c r="F20" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="45" t="s">
+      <c r="G20" s="58" t="s">
         <v>268</v>
       </c>
-      <c r="H20" s="45"/>
+      <c r="H20" s="58"/>
       <c r="I20" s="16" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="21" spans="2:9">
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45" t="s">
+      <c r="C21" s="58"/>
+      <c r="D21" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="E21" s="45"/>
+      <c r="E21" s="58"/>
       <c r="F21" s="16"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="58"/>
       <c r="I21" s="16" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45" t="s">
+      <c r="C22" s="58"/>
+      <c r="D22" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="45"/>
+      <c r="E22" s="58"/>
       <c r="F22" s="16"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
       <c r="I22" s="16" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="45" t="s">
+      <c r="B23" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45" t="s">
+      <c r="C23" s="58"/>
+      <c r="D23" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="45"/>
+      <c r="E23" s="58"/>
       <c r="F23" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="G23" s="45" t="s">
+      <c r="G23" s="58" t="s">
         <v>268</v>
       </c>
-      <c r="H23" s="45"/>
+      <c r="H23" s="58"/>
       <c r="I23" s="16" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45" t="s">
+      <c r="C24" s="58"/>
+      <c r="D24" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="45"/>
+      <c r="E24" s="58"/>
       <c r="F24" s="16"/>
-      <c r="G24" s="45" t="s">
+      <c r="G24" s="58" t="s">
         <v>271</v>
       </c>
-      <c r="H24" s="45"/>
+      <c r="H24" s="58"/>
       <c r="I24" s="16" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46" t="s">
+      <c r="C26" s="60"/>
+      <c r="D26" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
       <c r="I26" s="15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="58" t="s">
         <v>275</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="51" t="s">
+      <c r="C27" s="58"/>
+      <c r="D27" s="61" t="s">
         <v>276</v>
       </c>
-      <c r="E27" s="52"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="53"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="63"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="58" t="s">
         <v>277</v>
       </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45" t="s">
+      <c r="C28" s="58"/>
+      <c r="D28" s="58" t="s">
         <v>278</v>
       </c>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="55" t="s">
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="41" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="45" t="s">
+      <c r="B29" s="58" t="s">
         <v>277</v>
       </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45" t="s">
+      <c r="C29" s="58"/>
+      <c r="D29" s="58" t="s">
         <v>279</v>
       </c>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="55" t="s">
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="41" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="45" t="s">
+      <c r="B30" s="58" t="s">
         <v>280</v>
       </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45" t="s">
+      <c r="C30" s="58"/>
+      <c r="D30" s="58" t="s">
         <v>281</v>
       </c>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="55" t="s">
+      <c r="E30" s="58"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="41" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="49"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="50"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="64"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="39"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="46" t="s">
+      <c r="B32" s="60" t="s">
         <v>283</v>
       </c>
-      <c r="C32" s="46"/>
-      <c r="D32" s="46" t="s">
+      <c r="C32" s="60"/>
+      <c r="D32" s="60" t="s">
         <v>284</v>
       </c>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="46"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
       <c r="I32" s="15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="61" t="s">
         <v>285</v>
       </c>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="54" t="s">
+      <c r="C33" s="62"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="62"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="62"/>
+      <c r="I33" s="40" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="46" t="s">
+      <c r="B35" s="60" t="s">
         <v>282</v>
       </c>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46" t="s">
+      <c r="C35" s="60"/>
+      <c r="D35" s="60" t="s">
         <v>290</v>
       </c>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="60"/>
       <c r="I35" s="15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="23" customHeight="1">
-      <c r="B36" s="45" t="s">
+      <c r="B36" s="58" t="s">
         <v>275</v>
       </c>
-      <c r="C36" s="45"/>
-      <c r="D36" s="43" t="s">
+      <c r="C36" s="58"/>
+      <c r="D36" s="55" t="s">
         <v>291</v>
       </c>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="56" t="s">
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="59" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="45" t="s">
+      <c r="B37" s="58" t="s">
         <v>292</v>
       </c>
-      <c r="C37" s="45"/>
-      <c r="D37" s="43" t="s">
+      <c r="C37" s="58"/>
+      <c r="D37" s="55" t="s">
         <v>293</v>
       </c>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="57"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="56"/>
     </row>
     <row r="38" spans="2:9" ht="24" customHeight="1">
-      <c r="B38" s="45" t="s">
+      <c r="B38" s="58" t="s">
         <v>294</v>
       </c>
-      <c r="C38" s="45"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="43"/>
-      <c r="I38" s="57" t="s">
+      <c r="C38" s="58"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="56" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="45" t="s">
+      <c r="B39" s="58" t="s">
         <v>295</v>
       </c>
-      <c r="C39" s="45"/>
-      <c r="D39" s="43" t="s">
+      <c r="C39" s="58"/>
+      <c r="D39" s="55" t="s">
         <v>296</v>
       </c>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="57"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="56"/>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="43" t="s">
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="55" t="s">
         <v>297</v>
       </c>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="43"/>
-      <c r="I40" s="57" t="s">
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="56" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="45"/>
-      <c r="C41" s="45"/>
-      <c r="D41" s="43" t="s">
+      <c r="B41" s="58"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="55" t="s">
         <v>298</v>
       </c>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="57"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="56"/>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="45"/>
-      <c r="C42" s="45"/>
-      <c r="D42" s="43" t="s">
+      <c r="B42" s="58"/>
+      <c r="C42" s="58"/>
+      <c r="D42" s="55" t="s">
         <v>299</v>
       </c>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="57" t="s">
+      <c r="E42" s="55"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="56" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="45"/>
-      <c r="C43" s="45"/>
-      <c r="D43" s="43" t="s">
+      <c r="B43" s="58"/>
+      <c r="C43" s="58"/>
+      <c r="D43" s="55" t="s">
         <v>300</v>
       </c>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="43"/>
-      <c r="I43" s="57"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="56"/>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="45"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="43" t="s">
+      <c r="B44" s="58"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="55" t="s">
         <v>301</v>
       </c>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="57" t="s">
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="56" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="45" spans="2:9">
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="43" t="s">
+      <c r="B45" s="58"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="55" t="s">
         <v>302</v>
       </c>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="57"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="56"/>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="45" t="s">
+      <c r="B46" s="58" t="s">
         <v>303</v>
       </c>
-      <c r="C46" s="45"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="43"/>
-      <c r="I46" s="57" t="s">
+      <c r="C46" s="58"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="55"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="56" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="45" t="s">
+      <c r="B47" s="58" t="s">
         <v>304</v>
       </c>
-      <c r="C47" s="45"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="43"/>
-      <c r="H47" s="43"/>
-      <c r="I47" s="58"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="55"/>
+      <c r="E47" s="55"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="55"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="57"/>
     </row>
     <row r="51" spans="2:9" ht="37">
-      <c r="B51" s="44" t="s">
+      <c r="B51" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="C51" s="44"/>
-      <c r="D51" s="44"/>
-      <c r="E51" s="44"/>
+      <c r="C51" s="65"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
     </row>
     <row r="52" spans="2:9">
-      <c r="B52" s="42" t="s">
+      <c r="B52" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="C52" s="42"/>
-      <c r="D52" s="39" t="s">
+      <c r="C52" s="66"/>
+      <c r="D52" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="40"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="53"/>
       <c r="I52" s="4" t="s">
         <v>1</v>
       </c>
@@ -14707,13 +14653,13 @@
       <c r="C54" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="43" t="s">
+      <c r="D54" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="E54" s="43"/>
-      <c r="F54" s="43"/>
-      <c r="G54" s="43"/>
-      <c r="H54" s="43"/>
+      <c r="E54" s="55"/>
+      <c r="F54" s="55"/>
+      <c r="G54" s="55"/>
+      <c r="H54" s="55"/>
       <c r="I54" s="9" t="s">
         <v>12</v>
       </c>
@@ -14722,17 +14668,17 @@
       <c r="C55" s="17"/>
     </row>
     <row r="56" spans="2:9">
-      <c r="B56" s="42" t="s">
+      <c r="B56" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="C56" s="42"/>
-      <c r="D56" s="39" t="s">
+      <c r="C56" s="66"/>
+      <c r="D56" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
-      <c r="H56" s="40"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="53"/>
       <c r="I56" s="4" t="s">
         <v>1</v>
       </c>
@@ -14770,13 +14716,13 @@
       <c r="C58" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D58" s="43" t="s">
+      <c r="D58" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="E58" s="43"/>
-      <c r="F58" s="43"/>
-      <c r="G58" s="43"/>
-      <c r="H58" s="43"/>
+      <c r="E58" s="55"/>
+      <c r="F58" s="55"/>
+      <c r="G58" s="55"/>
+      <c r="H58" s="55"/>
       <c r="I58" s="9"/>
     </row>
     <row r="59" spans="2:9">
@@ -14987,17 +14933,17 @@
       <c r="C69" s="17"/>
     </row>
     <row r="70" spans="2:9">
-      <c r="B70" s="39" t="s">
+      <c r="B70" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C70" s="40"/>
-      <c r="D70" s="39" t="s">
+      <c r="C70" s="53"/>
+      <c r="D70" s="52" t="s">
         <v>331</v>
       </c>
-      <c r="E70" s="41"/>
-      <c r="F70" s="41"/>
-      <c r="G70" s="41"/>
-      <c r="H70" s="40"/>
+      <c r="E70" s="54"/>
+      <c r="F70" s="54"/>
+      <c r="G70" s="54"/>
+      <c r="H70" s="53"/>
       <c r="I70" s="10"/>
     </row>
     <row r="71" spans="2:9" s="1" customFormat="1">
@@ -15033,13 +14979,13 @@
       <c r="C72" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D72" s="43" t="s">
+      <c r="D72" s="55" t="s">
         <v>311</v>
       </c>
-      <c r="E72" s="43"/>
-      <c r="F72" s="43"/>
-      <c r="G72" s="43"/>
-      <c r="H72" s="43"/>
+      <c r="E72" s="55"/>
+      <c r="F72" s="55"/>
+      <c r="G72" s="55"/>
+      <c r="H72" s="55"/>
       <c r="I72" s="9" t="s">
         <v>332</v>
       </c>
@@ -15267,17 +15213,17 @@
       </c>
     </row>
     <row r="84" spans="2:9">
-      <c r="B84" s="39" t="s">
+      <c r="B84" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C84" s="40"/>
-      <c r="D84" s="39" t="s">
+      <c r="C84" s="53"/>
+      <c r="D84" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="E84" s="41"/>
-      <c r="F84" s="41"/>
-      <c r="G84" s="41"/>
-      <c r="H84" s="40"/>
+      <c r="E84" s="54"/>
+      <c r="F84" s="54"/>
+      <c r="G84" s="54"/>
+      <c r="H84" s="53"/>
       <c r="I84" s="10"/>
     </row>
     <row r="85" spans="2:9" s="1" customFormat="1">
@@ -15313,13 +15259,13 @@
       <c r="C86" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D86" s="43" t="s">
+      <c r="D86" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="E86" s="43"/>
-      <c r="F86" s="43"/>
-      <c r="G86" s="43"/>
-      <c r="H86" s="43"/>
+      <c r="E86" s="55"/>
+      <c r="F86" s="55"/>
+      <c r="G86" s="55"/>
+      <c r="H86" s="55"/>
       <c r="I86" s="9" t="s">
         <v>362</v>
       </c>
@@ -15537,17 +15483,17 @@
       </c>
     </row>
     <row r="98" spans="2:10">
-      <c r="B98" s="39" t="s">
+      <c r="B98" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C98" s="40"/>
-      <c r="D98" s="39" t="s">
+      <c r="C98" s="53"/>
+      <c r="D98" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="E98" s="41"/>
-      <c r="F98" s="41"/>
-      <c r="G98" s="41"/>
-      <c r="H98" s="40"/>
+      <c r="E98" s="54"/>
+      <c r="F98" s="54"/>
+      <c r="G98" s="54"/>
+      <c r="H98" s="53"/>
       <c r="I98" s="10"/>
     </row>
     <row r="99" spans="2:10">
@@ -15584,13 +15530,13 @@
       <c r="C100" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D100" s="43" t="s">
+      <c r="D100" s="55" t="s">
         <v>366</v>
       </c>
-      <c r="E100" s="43"/>
-      <c r="F100" s="43"/>
-      <c r="G100" s="43"/>
-      <c r="H100" s="43"/>
+      <c r="E100" s="55"/>
+      <c r="F100" s="55"/>
+      <c r="G100" s="55"/>
+      <c r="H100" s="55"/>
       <c r="I100" s="9" t="s">
         <v>362</v>
       </c>
@@ -15933,17 +15879,17 @@
       </c>
     </row>
     <row r="118" spans="2:9">
-      <c r="B118" s="39" t="s">
+      <c r="B118" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C118" s="40"/>
-      <c r="D118" s="39" t="s">
+      <c r="C118" s="53"/>
+      <c r="D118" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="E118" s="41"/>
-      <c r="F118" s="41"/>
-      <c r="G118" s="41"/>
-      <c r="H118" s="40"/>
+      <c r="E118" s="54"/>
+      <c r="F118" s="54"/>
+      <c r="G118" s="54"/>
+      <c r="H118" s="53"/>
       <c r="I118" s="10"/>
     </row>
     <row r="119" spans="2:9">
@@ -15979,13 +15925,13 @@
       <c r="C120" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D120" s="43" t="s">
+      <c r="D120" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="E120" s="43"/>
-      <c r="F120" s="43"/>
-      <c r="G120" s="43"/>
-      <c r="H120" s="43"/>
+      <c r="E120" s="55"/>
+      <c r="F120" s="55"/>
+      <c r="G120" s="55"/>
+      <c r="H120" s="55"/>
       <c r="I120" s="9" t="s">
         <v>362</v>
       </c>
@@ -16247,17 +16193,17 @@
       </c>
     </row>
     <row r="134" spans="2:9">
-      <c r="B134" s="39" t="s">
+      <c r="B134" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C134" s="40"/>
-      <c r="D134" s="39" t="s">
+      <c r="C134" s="53"/>
+      <c r="D134" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="E134" s="41"/>
-      <c r="F134" s="41"/>
-      <c r="G134" s="41"/>
-      <c r="H134" s="40"/>
+      <c r="E134" s="54"/>
+      <c r="F134" s="54"/>
+      <c r="G134" s="54"/>
+      <c r="H134" s="53"/>
       <c r="I134" s="10"/>
     </row>
     <row r="135" spans="2:9">
@@ -16293,13 +16239,13 @@
       <c r="C136" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D136" s="43" t="s">
+      <c r="D136" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="E136" s="43"/>
-      <c r="F136" s="43"/>
-      <c r="G136" s="43"/>
-      <c r="H136" s="43"/>
+      <c r="E136" s="55"/>
+      <c r="F136" s="55"/>
+      <c r="G136" s="55"/>
+      <c r="H136" s="55"/>
       <c r="I136" s="9" t="s">
         <v>362</v>
       </c>
@@ -16627,17 +16573,17 @@
       </c>
     </row>
     <row r="153" spans="2:9">
-      <c r="B153" s="39" t="s">
+      <c r="B153" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C153" s="40"/>
-      <c r="D153" s="39" t="s">
+      <c r="C153" s="53"/>
+      <c r="D153" s="52" t="s">
         <v>382</v>
       </c>
-      <c r="E153" s="41"/>
-      <c r="F153" s="41"/>
-      <c r="G153" s="41"/>
-      <c r="H153" s="40"/>
+      <c r="E153" s="54"/>
+      <c r="F153" s="54"/>
+      <c r="G153" s="54"/>
+      <c r="H153" s="53"/>
       <c r="I153" s="10"/>
     </row>
     <row r="154" spans="2:9">
@@ -16673,13 +16619,13 @@
       <c r="C155" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D155" s="43" t="s">
+      <c r="D155" s="55" t="s">
         <v>308</v>
       </c>
-      <c r="E155" s="43"/>
-      <c r="F155" s="43"/>
-      <c r="G155" s="43"/>
-      <c r="H155" s="43"/>
+      <c r="E155" s="55"/>
+      <c r="F155" s="55"/>
+      <c r="G155" s="55"/>
+      <c r="H155" s="55"/>
       <c r="I155" s="9" t="s">
         <v>383</v>
       </c>
@@ -16870,17 +16816,17 @@
       <c r="E165" s="2"/>
     </row>
     <row r="166" spans="2:9">
-      <c r="B166" s="39" t="s">
+      <c r="B166" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C166" s="40"/>
-      <c r="D166" s="39" t="s">
+      <c r="C166" s="53"/>
+      <c r="D166" s="52" t="s">
         <v>382</v>
       </c>
-      <c r="E166" s="41"/>
-      <c r="F166" s="41"/>
-      <c r="G166" s="41"/>
-      <c r="H166" s="40"/>
+      <c r="E166" s="54"/>
+      <c r="F166" s="54"/>
+      <c r="G166" s="54"/>
+      <c r="H166" s="53"/>
       <c r="I166" s="10"/>
     </row>
     <row r="167" spans="2:9">
@@ -16916,13 +16862,13 @@
       <c r="C168" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D168" s="43" t="s">
+      <c r="D168" s="55" t="s">
         <v>305</v>
       </c>
-      <c r="E168" s="43"/>
-      <c r="F168" s="43"/>
-      <c r="G168" s="43"/>
-      <c r="H168" s="43"/>
+      <c r="E168" s="55"/>
+      <c r="F168" s="55"/>
+      <c r="G168" s="55"/>
+      <c r="H168" s="55"/>
       <c r="I168" s="9" t="s">
         <v>407</v>
       </c>
@@ -16978,7 +16924,7 @@
       <c r="C171" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D171" s="59" t="s">
+      <c r="D171" s="42" t="s">
         <v>333</v>
       </c>
       <c r="E171" s="8" t="s">
@@ -17000,7 +16946,7 @@
       <c r="C172" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D172" s="59" t="s">
+      <c r="D172" s="42" t="s">
         <v>333</v>
       </c>
       <c r="E172" s="8" t="s">
@@ -17283,17 +17229,17 @@
       <c r="L183" s="3"/>
     </row>
     <row r="185" spans="1:12">
-      <c r="B185" s="39" t="s">
+      <c r="B185" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C185" s="40"/>
-      <c r="D185" s="39" t="s">
+      <c r="C185" s="53"/>
+      <c r="D185" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="E185" s="41"/>
-      <c r="F185" s="41"/>
-      <c r="G185" s="41"/>
-      <c r="H185" s="40"/>
+      <c r="E185" s="54"/>
+      <c r="F185" s="54"/>
+      <c r="G185" s="54"/>
+      <c r="H185" s="53"/>
       <c r="I185" s="10"/>
     </row>
     <row r="186" spans="1:12">
@@ -17329,13 +17275,13 @@
       <c r="C187" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D187" s="43" t="s">
+      <c r="D187" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="E187" s="43"/>
-      <c r="F187" s="43"/>
-      <c r="G187" s="43"/>
-      <c r="H187" s="43"/>
+      <c r="E187" s="55"/>
+      <c r="F187" s="55"/>
+      <c r="G187" s="55"/>
+      <c r="H187" s="55"/>
       <c r="I187" s="9" t="s">
         <v>429</v>
       </c>
@@ -17391,7 +17337,7 @@
       <c r="C190" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D190" s="59" t="s">
+      <c r="D190" s="42" t="s">
         <v>333</v>
       </c>
       <c r="E190" s="8" t="s">
@@ -17413,7 +17359,7 @@
       <c r="C191" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D191" s="59" t="s">
+      <c r="D191" s="42" t="s">
         <v>333</v>
       </c>
       <c r="E191" s="8" t="s">
@@ -17592,17 +17538,17 @@
       <c r="L198" s="3"/>
     </row>
     <row r="200" spans="1:12">
-      <c r="B200" s="39" t="s">
+      <c r="B200" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C200" s="40"/>
-      <c r="D200" s="39" t="s">
+      <c r="C200" s="53"/>
+      <c r="D200" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="E200" s="41"/>
-      <c r="F200" s="41"/>
-      <c r="G200" s="41"/>
-      <c r="H200" s="40"/>
+      <c r="E200" s="54"/>
+      <c r="F200" s="54"/>
+      <c r="G200" s="54"/>
+      <c r="H200" s="53"/>
       <c r="I200" s="10"/>
     </row>
     <row r="201" spans="1:12">
@@ -17638,13 +17584,13 @@
       <c r="C202" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D202" s="43" t="s">
+      <c r="D202" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="E202" s="43"/>
-      <c r="F202" s="43"/>
-      <c r="G202" s="43"/>
-      <c r="H202" s="43"/>
+      <c r="E202" s="55"/>
+      <c r="F202" s="55"/>
+      <c r="G202" s="55"/>
+      <c r="H202" s="55"/>
       <c r="I202" s="9" t="s">
         <v>452</v>
       </c>
@@ -17759,17 +17705,17 @@
       <c r="L206" s="3"/>
     </row>
     <row r="208" spans="1:12">
-      <c r="B208" s="39" t="s">
+      <c r="B208" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C208" s="40"/>
-      <c r="D208" s="39" t="s">
+      <c r="C208" s="53"/>
+      <c r="D208" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="E208" s="41"/>
-      <c r="F208" s="41"/>
-      <c r="G208" s="41"/>
-      <c r="H208" s="40"/>
+      <c r="E208" s="54"/>
+      <c r="F208" s="54"/>
+      <c r="G208" s="54"/>
+      <c r="H208" s="53"/>
       <c r="I208" s="10"/>
     </row>
     <row r="209" spans="1:12">
@@ -17805,13 +17751,13 @@
       <c r="C210" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D210" s="43" t="s">
+      <c r="D210" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="E210" s="43"/>
-      <c r="F210" s="43"/>
-      <c r="G210" s="43"/>
-      <c r="H210" s="43"/>
+      <c r="E210" s="55"/>
+      <c r="F210" s="55"/>
+      <c r="G210" s="55"/>
+      <c r="H210" s="55"/>
       <c r="I210" s="9" t="s">
         <v>459</v>
       </c>
@@ -17901,17 +17847,17 @@
       <c r="L213" s="3"/>
     </row>
     <row r="215" spans="1:12">
-      <c r="B215" s="39" t="s">
+      <c r="B215" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C215" s="40"/>
-      <c r="D215" s="39" t="s">
+      <c r="C215" s="53"/>
+      <c r="D215" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="E215" s="41"/>
-      <c r="F215" s="41"/>
-      <c r="G215" s="41"/>
-      <c r="H215" s="40"/>
+      <c r="E215" s="54"/>
+      <c r="F215" s="54"/>
+      <c r="G215" s="54"/>
+      <c r="H215" s="53"/>
       <c r="I215" s="10"/>
     </row>
     <row r="216" spans="1:12">
@@ -17947,13 +17893,13 @@
       <c r="C217" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D217" s="43" t="s">
+      <c r="D217" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="E217" s="43"/>
-      <c r="F217" s="43"/>
-      <c r="G217" s="43"/>
-      <c r="H217" s="43"/>
+      <c r="E217" s="55"/>
+      <c r="F217" s="55"/>
+      <c r="G217" s="55"/>
+      <c r="H217" s="55"/>
       <c r="I217" s="9" t="s">
         <v>469</v>
       </c>
@@ -18065,111 +18011,6 @@
     </row>
   </sheetData>
   <mergeCells count="146">
-    <mergeCell ref="B215:C215"/>
-    <mergeCell ref="D215:H215"/>
-    <mergeCell ref="D217:H217"/>
-    <mergeCell ref="B185:C185"/>
-    <mergeCell ref="D185:H185"/>
-    <mergeCell ref="D187:H187"/>
-    <mergeCell ref="B200:C200"/>
-    <mergeCell ref="D200:H200"/>
-    <mergeCell ref="D202:H202"/>
-    <mergeCell ref="B208:C208"/>
-    <mergeCell ref="D208:H208"/>
-    <mergeCell ref="D210:H210"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="D118:H118"/>
-    <mergeCell ref="B166:C166"/>
-    <mergeCell ref="D166:H166"/>
-    <mergeCell ref="D168:H168"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="I42:I43"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D120:H120"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="D155:H155"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="D70:H70"/>
-    <mergeCell ref="D72:H72"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D98:H98"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="D134:H134"/>
-    <mergeCell ref="D136:H136"/>
-    <mergeCell ref="D84:H84"/>
-    <mergeCell ref="D86:H86"/>
-    <mergeCell ref="D100:H100"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G13:H13"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:E22"/>
@@ -18194,23 +18035,128 @@
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="G14:H14"/>
-    <mergeCell ref="B153:C153"/>
-    <mergeCell ref="D153:H153"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="D134:H134"/>
+    <mergeCell ref="D136:H136"/>
+    <mergeCell ref="D84:H84"/>
+    <mergeCell ref="D86:H86"/>
+    <mergeCell ref="D100:H100"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="D56:H56"/>
     <mergeCell ref="D58:H58"/>
     <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="G31:H31"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="G24:H24"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D54:H54"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:H11"/>
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D120:H120"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="D70:H70"/>
+    <mergeCell ref="D72:H72"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D98:H98"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="D118:H118"/>
+    <mergeCell ref="B166:C166"/>
+    <mergeCell ref="D166:H166"/>
+    <mergeCell ref="D168:H168"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D155:H155"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="D153:H153"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="B215:C215"/>
+    <mergeCell ref="D215:H215"/>
+    <mergeCell ref="D217:H217"/>
+    <mergeCell ref="B185:C185"/>
+    <mergeCell ref="D185:H185"/>
+    <mergeCell ref="D187:H187"/>
+    <mergeCell ref="B200:C200"/>
+    <mergeCell ref="D200:H200"/>
+    <mergeCell ref="D202:H202"/>
+    <mergeCell ref="B208:C208"/>
+    <mergeCell ref="D208:H208"/>
+    <mergeCell ref="D210:H210"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18229,11 +18175,11 @@
   <sheetData>
     <row r="3" spans="1:12" s="3" customFormat="1" ht="27">
       <c r="A3" s="1"/>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="68" t="s">
         <v>254</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
       <c r="E3" s="35"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -18264,10 +18210,10 @@
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" ht="23">
       <c r="B6" s="38"/>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="D6" s="48"/>
+      <c r="D6" s="67"/>
       <c r="E6" s="2" t="s">
         <v>163</v>
       </c>
@@ -18276,10 +18222,10 @@
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" ht="23">
       <c r="B7" s="38"/>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="67" t="s">
         <v>161</v>
       </c>
-      <c r="D7" s="48"/>
+      <c r="D7" s="67"/>
       <c r="E7" s="2" t="s">
         <v>168</v>
       </c>
@@ -18288,10 +18234,10 @@
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" ht="23">
       <c r="B8" s="38"/>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="D8" s="48"/>
+      <c r="D8" s="67"/>
       <c r="E8" s="2" t="s">
         <v>167</v>
       </c>
@@ -18300,10 +18246,10 @@
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" ht="23">
       <c r="B9" s="38"/>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="D9" s="48"/>
+      <c r="D9" s="67"/>
       <c r="E9" s="2" t="s">
         <v>166</v>
       </c>
@@ -18322,10 +18268,10 @@
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" ht="23">
       <c r="B11" s="37"/>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="67" t="s">
         <v>213</v>
       </c>
-      <c r="D11" s="48"/>
+      <c r="D11" s="67"/>
       <c r="E11" s="2" t="s">
         <v>214</v>
       </c>
@@ -18334,10 +18280,10 @@
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" ht="23">
       <c r="B12" s="38"/>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="67" t="s">
         <v>172</v>
       </c>
-      <c r="D12" s="48"/>
+      <c r="D12" s="67"/>
       <c r="E12" s="2" t="s">
         <v>173</v>
       </c>
@@ -18346,10 +18292,10 @@
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" ht="23">
       <c r="B13" s="38"/>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="67" t="s">
         <v>174</v>
       </c>
-      <c r="D13" s="48"/>
+      <c r="D13" s="67"/>
       <c r="E13" s="2" t="s">
         <v>175</v>
       </c>
@@ -18367,10 +18313,10 @@
       <c r="L14" s="22"/>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" ht="23">
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="67" t="s">
         <v>178</v>
       </c>
-      <c r="D15" s="48"/>
+      <c r="D15" s="67"/>
       <c r="E15" s="2" t="s">
         <v>203</v>
       </c>
@@ -18378,10 +18324,10 @@
       <c r="L15" s="22"/>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" ht="23">
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="67" t="s">
         <v>179</v>
       </c>
-      <c r="D16" s="48"/>
+      <c r="D16" s="67"/>
       <c r="E16" s="2" t="s">
         <v>204</v>
       </c>
@@ -18391,10 +18337,10 @@
     <row r="17" spans="1:15" s="3" customFormat="1" ht="23">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="48" t="s">
+      <c r="C17" s="67" t="s">
         <v>180</v>
       </c>
-      <c r="D17" s="48"/>
+      <c r="D17" s="67"/>
       <c r="E17" s="2" t="s">
         <v>205</v>
       </c>
@@ -18408,10 +18354,10 @@
     <row r="18" spans="1:15" s="3" customFormat="1" ht="23">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="67" t="s">
         <v>181</v>
       </c>
-      <c r="D18" s="48"/>
+      <c r="D18" s="67"/>
       <c r="E18" s="2" t="s">
         <v>182</v>
       </c>
@@ -18437,11 +18383,11 @@
     </row>
     <row r="20" spans="1:15" s="3" customFormat="1" ht="27">
       <c r="A20" s="1"/>
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="68" t="s">
         <v>255</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
       <c r="E20" s="35"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -18504,11 +18450,11 @@
       </c>
     </row>
     <row r="26" spans="1:15" s="2" customFormat="1" ht="27">
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="68" t="s">
         <v>256</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
       <c r="E26" s="35"/>
       <c r="K26" s="22"/>
       <c r="L26" s="22"/>
@@ -18524,10 +18470,10 @@
       <c r="L27" s="22"/>
     </row>
     <row r="28" spans="1:15" s="2" customFormat="1" ht="23">
-      <c r="C28" s="48" t="s">
+      <c r="C28" s="67" t="s">
         <v>193</v>
       </c>
-      <c r="D28" s="48"/>
+      <c r="D28" s="67"/>
       <c r="E28" s="2" t="s">
         <v>194</v>
       </c>
@@ -18535,10 +18481,10 @@
       <c r="L28" s="22"/>
     </row>
     <row r="29" spans="1:15" s="2" customFormat="1" ht="23">
-      <c r="C29" s="48" t="s">
+      <c r="C29" s="67" t="s">
         <v>195</v>
       </c>
-      <c r="D29" s="48"/>
+      <c r="D29" s="67"/>
       <c r="E29" s="2" t="s">
         <v>196</v>
       </c>
@@ -18546,10 +18492,10 @@
       <c r="L29" s="22"/>
     </row>
     <row r="30" spans="1:15" s="2" customFormat="1" ht="23">
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="67" t="s">
         <v>197</v>
       </c>
-      <c r="D30" s="48"/>
+      <c r="D30" s="67"/>
       <c r="E30" s="2" t="s">
         <v>198</v>
       </c>
@@ -18557,10 +18503,10 @@
       <c r="L30" s="22"/>
     </row>
     <row r="31" spans="1:15" s="2" customFormat="1" ht="23">
-      <c r="C31" s="48" t="s">
+      <c r="C31" s="67" t="s">
         <v>199</v>
       </c>
-      <c r="D31" s="48"/>
+      <c r="D31" s="67"/>
       <c r="E31" s="2" t="s">
         <v>200</v>
       </c>
@@ -18568,10 +18514,10 @@
       <c r="L31" s="22"/>
     </row>
     <row r="32" spans="1:15" s="2" customFormat="1" ht="23">
-      <c r="C32" s="48" t="s">
+      <c r="C32" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="D32" s="48"/>
+      <c r="D32" s="67"/>
       <c r="E32" s="2" t="s">
         <v>202</v>
       </c>
@@ -18583,11 +18529,11 @@
       <c r="L33" s="22"/>
     </row>
     <row r="34" spans="2:12" s="2" customFormat="1" ht="27">
-      <c r="B34" s="47" t="s">
+      <c r="B34" s="68" t="s">
         <v>257</v>
       </c>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="68"/>
       <c r="E34" s="35"/>
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
@@ -18603,10 +18549,10 @@
       <c r="L35" s="22"/>
     </row>
     <row r="36" spans="2:12" s="2" customFormat="1" ht="23">
-      <c r="C36" s="48" t="s">
+      <c r="C36" s="67" t="s">
         <v>208</v>
       </c>
-      <c r="D36" s="48"/>
+      <c r="D36" s="67"/>
       <c r="E36" s="2" t="s">
         <v>209</v>
       </c>
@@ -18614,10 +18560,10 @@
       <c r="L36" s="22"/>
     </row>
     <row r="37" spans="2:12" s="2" customFormat="1" ht="23">
-      <c r="C37" s="48" t="s">
+      <c r="C37" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="D37" s="48"/>
+      <c r="D37" s="67"/>
       <c r="E37" s="2" t="s">
         <v>260</v>
       </c>
@@ -18625,10 +18571,10 @@
       <c r="L37" s="22"/>
     </row>
     <row r="38" spans="2:12" s="2" customFormat="1" ht="23">
-      <c r="C38" s="48" t="s">
+      <c r="C38" s="67" t="s">
         <v>211</v>
       </c>
-      <c r="D38" s="48"/>
+      <c r="D38" s="67"/>
       <c r="E38" s="2" t="s">
         <v>212</v>
       </c>
@@ -18636,8 +18582,8 @@
       <c r="L38" s="22"/>
     </row>
     <row r="39" spans="2:12" s="2" customFormat="1" ht="23">
-      <c r="C39" s="48"/>
-      <c r="D39" s="48"/>
+      <c r="C39" s="67"/>
+      <c r="D39" s="67"/>
       <c r="K39" s="22"/>
       <c r="L39" s="22"/>
     </row>
@@ -18652,10 +18598,10 @@
       <c r="L40" s="22"/>
     </row>
     <row r="41" spans="2:12" s="2" customFormat="1" ht="23">
-      <c r="C41" s="48" t="s">
+      <c r="C41" s="67" t="s">
         <v>217</v>
       </c>
-      <c r="D41" s="48"/>
+      <c r="D41" s="67"/>
       <c r="E41" s="2" t="s">
         <v>218</v>
       </c>
@@ -18663,10 +18609,10 @@
       <c r="L41" s="22"/>
     </row>
     <row r="42" spans="2:12" s="2" customFormat="1" ht="23">
-      <c r="C42" s="48" t="s">
+      <c r="C42" s="67" t="s">
         <v>161</v>
       </c>
-      <c r="D42" s="48"/>
+      <c r="D42" s="67"/>
       <c r="E42" s="2" t="s">
         <v>219</v>
       </c>
@@ -18674,10 +18620,10 @@
       <c r="L42" s="22"/>
     </row>
     <row r="43" spans="2:12" s="2" customFormat="1" ht="23">
-      <c r="C43" s="48" t="s">
+      <c r="C43" s="67" t="s">
         <v>220</v>
       </c>
-      <c r="D43" s="48"/>
+      <c r="D43" s="67"/>
       <c r="E43" s="2" t="s">
         <v>221</v>
       </c>
@@ -18685,10 +18631,10 @@
       <c r="L43" s="22"/>
     </row>
     <row r="44" spans="2:12" s="2" customFormat="1" ht="23">
-      <c r="C44" s="48" t="s">
+      <c r="C44" s="67" t="s">
         <v>222</v>
       </c>
-      <c r="D44" s="48"/>
+      <c r="D44" s="67"/>
       <c r="E44" s="2" t="s">
         <v>223</v>
       </c>
@@ -18700,11 +18646,11 @@
       <c r="L45" s="22"/>
     </row>
     <row r="46" spans="2:12" s="2" customFormat="1" ht="27">
-      <c r="B46" s="47" t="s">
+      <c r="B46" s="68" t="s">
         <v>258</v>
       </c>
-      <c r="C46" s="47"/>
-      <c r="D46" s="47"/>
+      <c r="C46" s="68"/>
+      <c r="D46" s="68"/>
       <c r="E46" s="35"/>
       <c r="K46" s="22"/>
       <c r="L46" s="22"/>
@@ -18720,10 +18666,10 @@
       <c r="L47" s="22"/>
     </row>
     <row r="48" spans="2:12" s="2" customFormat="1" ht="23">
-      <c r="C48" s="48" t="s">
+      <c r="C48" s="67" t="s">
         <v>262</v>
       </c>
-      <c r="D48" s="48"/>
+      <c r="D48" s="67"/>
       <c r="E48" s="2" t="s">
         <v>261</v>
       </c>
@@ -18731,10 +18677,10 @@
       <c r="L48" s="22"/>
     </row>
     <row r="49" spans="1:12" s="2" customFormat="1" ht="23">
-      <c r="C49" s="48" t="s">
+      <c r="C49" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="D49" s="48"/>
+      <c r="D49" s="67"/>
       <c r="E49" s="2" t="s">
         <v>264</v>
       </c>
@@ -18744,10 +18690,10 @@
     <row r="50" spans="1:12" s="3" customFormat="1" ht="23">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
-      <c r="C50" s="48" t="s">
+      <c r="C50" s="67" t="s">
         <v>226</v>
       </c>
-      <c r="D50" s="48"/>
+      <c r="D50" s="67"/>
       <c r="E50" s="2" t="s">
         <v>227</v>
       </c>
@@ -18761,10 +18707,10 @@
     <row r="51" spans="1:12" s="3" customFormat="1" ht="23">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
-      <c r="C51" s="48" t="s">
+      <c r="C51" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="D51" s="48"/>
+      <c r="D51" s="67"/>
       <c r="E51" s="2" t="s">
         <v>229</v>
       </c>
@@ -18778,10 +18724,10 @@
     <row r="52" spans="1:12" s="3" customFormat="1" ht="23">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
-      <c r="C52" s="48" t="s">
+      <c r="C52" s="67" t="s">
         <v>230</v>
       </c>
-      <c r="D52" s="48"/>
+      <c r="D52" s="67"/>
       <c r="E52" s="2" t="s">
         <v>231</v>
       </c>
@@ -18812,10 +18758,10 @@
     <row r="54" spans="1:12" s="3" customFormat="1" ht="23">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
-      <c r="C54" s="48" t="s">
+      <c r="C54" s="67" t="s">
         <v>233</v>
       </c>
-      <c r="D54" s="48"/>
+      <c r="D54" s="67"/>
       <c r="E54" s="2" t="s">
         <v>234</v>
       </c>
@@ -18829,10 +18775,10 @@
     <row r="55" spans="1:12" s="3" customFormat="1" ht="23">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
-      <c r="C55" s="48" t="s">
+      <c r="C55" s="67" t="s">
         <v>222</v>
       </c>
-      <c r="D55" s="48"/>
+      <c r="D55" s="67"/>
       <c r="E55" s="2" t="s">
         <v>236</v>
       </c>
@@ -18846,10 +18792,10 @@
     <row r="56" spans="1:12" s="3" customFormat="1" ht="23">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
-      <c r="C56" s="48" t="s">
+      <c r="C56" s="67" t="s">
         <v>237</v>
       </c>
-      <c r="D56" s="48"/>
+      <c r="D56" s="67"/>
       <c r="E56" s="2" t="s">
         <v>246</v>
       </c>
@@ -18863,10 +18809,10 @@
     <row r="57" spans="1:12" s="3" customFormat="1" ht="23">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
-      <c r="C57" s="48" t="s">
+      <c r="C57" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="D57" s="48"/>
+      <c r="D57" s="67"/>
       <c r="E57" s="2" t="s">
         <v>245</v>
       </c>
@@ -18880,10 +18826,10 @@
     <row r="58" spans="1:12" s="3" customFormat="1" ht="23">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
-      <c r="C58" s="48" t="s">
+      <c r="C58" s="67" t="s">
         <v>239</v>
       </c>
-      <c r="D58" s="48"/>
+      <c r="D58" s="67"/>
       <c r="E58" s="2" t="s">
         <v>244</v>
       </c>
@@ -18897,10 +18843,10 @@
     <row r="59" spans="1:12" s="3" customFormat="1" ht="23">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
-      <c r="C59" s="48" t="s">
+      <c r="C59" s="67" t="s">
         <v>240</v>
       </c>
-      <c r="D59" s="48"/>
+      <c r="D59" s="67"/>
       <c r="E59" s="2" t="s">
         <v>242</v>
       </c>
@@ -18914,10 +18860,10 @@
     <row r="60" spans="1:12" s="3" customFormat="1" ht="23">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
-      <c r="C60" s="48" t="s">
+      <c r="C60" s="67" t="s">
         <v>241</v>
       </c>
-      <c r="D60" s="48"/>
+      <c r="D60" s="67"/>
       <c r="E60" s="2" t="s">
         <v>243</v>
       </c>
@@ -18931,10 +18877,10 @@
     <row r="61" spans="1:12" s="3" customFormat="1" ht="23">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
-      <c r="C61" s="48" t="s">
+      <c r="C61" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="D61" s="48"/>
+      <c r="D61" s="67"/>
       <c r="E61" s="2" t="s">
         <v>248</v>
       </c>
@@ -18948,10 +18894,10 @@
     <row r="62" spans="1:12" s="3" customFormat="1" ht="23">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="48" t="s">
+      <c r="C62" s="67" t="s">
         <v>249</v>
       </c>
-      <c r="D62" s="48"/>
+      <c r="D62" s="67"/>
       <c r="E62" s="2" t="s">
         <v>250</v>
       </c>
@@ -18964,11 +18910,11 @@
     </row>
     <row r="65" spans="1:12" s="3" customFormat="1" ht="27">
       <c r="A65" s="1"/>
-      <c r="B65" s="47" t="s">
+      <c r="B65" s="68" t="s">
         <v>259</v>
       </c>
-      <c r="C65" s="47"/>
-      <c r="D65" s="47"/>
+      <c r="C65" s="68"/>
+      <c r="D65" s="68"/>
       <c r="E65" s="35"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -18982,10 +18928,10 @@
       <c r="B66" s="36" t="s">
         <v>251</v>
       </c>
-      <c r="C66" s="48" t="s">
+      <c r="C66" s="67" t="s">
         <v>252</v>
       </c>
-      <c r="D66" s="48"/>
+      <c r="D66" s="67"/>
       <c r="E66" s="2" t="s">
         <v>253</v>
       </c>
@@ -18998,35 +18944,6 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="C52:D52"/>
@@ -19043,6 +18960,35 @@
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19050,293 +18996,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6C26D0D-500B-AA41-9E70-BC6C65DEE3CD}">
-  <dimension ref="B3:B152"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="23"/>
-  <cols>
-    <col min="2" max="2" width="89.625" style="60" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:2">
-      <c r="B3" s="67" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2">
-      <c r="B4" s="63" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" s="64" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2">
-      <c r="B7" s="67" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2">
-      <c r="B8" s="63" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2">
-      <c r="B9" s="64" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" s="67" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12" s="63" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="65" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="65" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2">
-      <c r="B15" s="65" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2">
-      <c r="B16" s="65" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="64" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="67" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="63" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" s="65" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="65" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" s="65" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24" s="64" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26" s="67" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27" s="63" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="65" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="65" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2">
-      <c r="B30" s="64" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2">
-      <c r="B32" s="67" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="63" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="65" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="65" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="64" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="67" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2">
-      <c r="B40" s="66" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2">
-      <c r="B42" s="67" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2">
-      <c r="B43" s="62" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2">
-      <c r="B45" s="68" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2">
-      <c r="B46" s="63" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" s="65" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2">
-      <c r="B48" s="65" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2">
-      <c r="B49" s="65" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2">
-      <c r="B50" s="64" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2">
-      <c r="B52" s="67" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" s="63" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2">
-      <c r="B54" s="65" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2">
-      <c r="B55" s="65" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2">
-      <c r="B56" s="64" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2">
-      <c r="B58" s="67" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2">
-      <c r="B59" s="63" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2">
-      <c r="B60" s="65" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2">
-      <c r="B61" s="64" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2">
-      <c r="B63" s="67" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2">
-      <c r="B64" s="62" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2">
-      <c r="B76" s="61"/>
-    </row>
-    <row r="97" spans="2:2">
-      <c r="B97" s="61"/>
-    </row>
-    <row r="106" spans="2:2">
-      <c r="B106" s="61"/>
-    </row>
-    <row r="116" spans="2:2">
-      <c r="B116" s="61"/>
-    </row>
-    <row r="129" spans="2:2">
-      <c r="B129" s="61"/>
-    </row>
-    <row r="139" spans="2:2">
-      <c r="B139" s="61"/>
-    </row>
-    <row r="152" spans="2:2">
-      <c r="B152" s="61"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C7EE81-A95B-1845-B00C-0771D6922203}">
-  <dimension ref="B1:AD197"/>
+  <dimension ref="B1:AD196"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="10" style="22"/>
@@ -19369,44 +19030,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:30" ht="23">
-      <c r="B1" s="76" t="s">
+      <c r="B1" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
     </row>
     <row r="2" spans="2:30" s="29" customFormat="1" ht="23">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
       <c r="S2" s="34"/>
       <c r="T2" s="28"/>
       <c r="U2" s="30"/>
@@ -19414,24 +19060,24 @@
       <c r="X2" s="33"/>
     </row>
     <row r="3" spans="2:30" s="29" customFormat="1" ht="23">
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="77"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="23"/>
+      <c r="O3"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
       <c r="S3" s="34"/>
       <c r="T3" s="28"/>
       <c r="U3" s="30"/>
@@ -19442,21 +19088,21 @@
       <c r="B4" s="18" t="s">
         <v>478</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="78"/>
-      <c r="L4" s="78"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="79"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="78"/>
-      <c r="Q4" s="78"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="23"/>
+      <c r="O4"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
       <c r="S4" s="31"/>
       <c r="T4" s="28"/>
       <c r="U4" s="30"/>
@@ -19464,112 +19110,37 @@
       <c r="X4" s="33"/>
     </row>
     <row r="5" spans="2:30" ht="23">
-      <c r="B5" s="76" t="s">
+      <c r="B5" s="50" t="s">
         <v>479</v>
       </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="80"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
       <c r="S5" s="27"/>
       <c r="AD5" s="22"/>
     </row>
     <row r="6" spans="2:30" ht="23">
-      <c r="B6" s="76" t="s">
+      <c r="B6" s="50" t="s">
         <v>480</v>
       </c>
-      <c r="C6" s="77"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="78"/>
-      <c r="L6" s="78"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="79"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="78"/>
-      <c r="Q6" s="78"/>
       <c r="S6" s="27"/>
       <c r="AD6" s="22"/>
     </row>
     <row r="7" spans="2:30" ht="23">
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="50" t="s">
         <v>481</v>
       </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="78"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
-      <c r="J7" s="78"/>
-      <c r="K7" s="78"/>
-      <c r="L7" s="78"/>
-      <c r="M7" s="77"/>
-      <c r="N7" s="79"/>
-      <c r="O7" s="80"/>
-      <c r="P7" s="78"/>
-      <c r="Q7" s="78"/>
       <c r="S7" s="27"/>
       <c r="AD7" s="22"/>
     </row>
     <row r="8" spans="2:30" ht="23">
-      <c r="B8" s="76" t="s">
+      <c r="B8" s="50" t="s">
         <v>482</v>
       </c>
-      <c r="C8" s="77"/>
-      <c r="D8" s="78"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="78"/>
-      <c r="I8" s="78"/>
-      <c r="J8" s="78"/>
-      <c r="K8" s="78"/>
-      <c r="L8" s="78"/>
-      <c r="M8" s="77"/>
-      <c r="N8" s="79"/>
-      <c r="O8" s="80"/>
-      <c r="P8" s="78"/>
-      <c r="Q8" s="78"/>
       <c r="S8" s="27"/>
       <c r="AD8" s="22"/>
     </row>
     <row r="9" spans="2:30" ht="23">
-      <c r="B9" s="76" t="s">
+      <c r="B9" s="50" t="s">
         <v>483</v>
       </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="78"/>
-      <c r="K9" s="78"/>
-      <c r="L9" s="78"/>
-      <c r="M9" s="77"/>
-      <c r="N9" s="79"/>
-      <c r="O9" s="80"/>
-      <c r="P9" s="78"/>
-      <c r="Q9" s="78"/>
       <c r="S9" s="27"/>
       <c r="AD9" s="22"/>
     </row>
@@ -19577,109 +19148,34 @@
       <c r="B10" s="18" t="s">
         <v>484</v>
       </c>
-      <c r="C10" s="77"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="78"/>
-      <c r="K10" s="78"/>
-      <c r="L10" s="78"/>
-      <c r="M10" s="77"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="80"/>
-      <c r="P10" s="78"/>
-      <c r="Q10" s="78"/>
       <c r="S10" s="27"/>
       <c r="AD10" s="22"/>
     </row>
     <row r="11" spans="2:30" ht="23">
-      <c r="B11" s="76" t="s">
+      <c r="B11" s="50" t="s">
         <v>485</v>
       </c>
-      <c r="C11" s="77"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="78"/>
-      <c r="K11" s="78"/>
-      <c r="L11" s="78"/>
-      <c r="M11" s="77"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="80"/>
-      <c r="P11" s="78"/>
-      <c r="Q11" s="78"/>
       <c r="S11" s="27"/>
       <c r="AD11" s="22"/>
     </row>
     <row r="12" spans="2:30" ht="23">
-      <c r="B12" s="76" t="s">
+      <c r="B12" s="50" t="s">
         <v>486</v>
       </c>
-      <c r="C12" s="77"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="77"/>
-      <c r="N12" s="79"/>
-      <c r="O12" s="80"/>
-      <c r="P12" s="78"/>
-      <c r="Q12" s="78"/>
       <c r="S12" s="27"/>
       <c r="AD12" s="22"/>
     </row>
     <row r="13" spans="2:30" ht="23">
-      <c r="B13" s="76" t="s">
+      <c r="B13" s="50" t="s">
         <v>487</v>
       </c>
-      <c r="C13" s="77"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="77"/>
-      <c r="N13" s="79"/>
-      <c r="O13" s="80"/>
-      <c r="P13" s="78"/>
-      <c r="Q13" s="78"/>
       <c r="S13" s="27"/>
       <c r="AD13" s="22"/>
     </row>
     <row r="14" spans="2:30" ht="23">
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="50" t="s">
         <v>483</v>
       </c>
-      <c r="C14" s="77"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="78"/>
-      <c r="M14" s="77"/>
-      <c r="N14" s="79"/>
-      <c r="O14" s="80"/>
-      <c r="P14" s="78"/>
-      <c r="Q14" s="78"/>
       <c r="S14" s="27"/>
       <c r="AD14" s="22"/>
     </row>
@@ -19687,153 +19183,48 @@
       <c r="B15" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="C15" s="77"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="78"/>
-      <c r="M15" s="77"/>
-      <c r="N15" s="79"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="78"/>
-      <c r="Q15" s="78"/>
       <c r="S15" s="27"/>
       <c r="AD15" s="22"/>
     </row>
     <row r="16" spans="2:30" ht="23">
-      <c r="B16" s="76" t="s">
+      <c r="B16" s="50" t="s">
         <v>489</v>
       </c>
-      <c r="C16" s="77"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="78"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="78"/>
-      <c r="M16" s="77"/>
-      <c r="N16" s="79"/>
-      <c r="O16" s="80"/>
-      <c r="P16" s="78"/>
-      <c r="Q16" s="78"/>
       <c r="S16" s="27"/>
       <c r="AD16" s="22"/>
     </row>
     <row r="17" spans="2:30" ht="23">
-      <c r="B17" s="76" t="s">
+      <c r="B17" s="50" t="s">
         <v>490</v>
       </c>
-      <c r="C17" s="77"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="77"/>
-      <c r="N17" s="79"/>
-      <c r="O17" s="80"/>
-      <c r="P17" s="78"/>
-      <c r="Q17" s="78"/>
       <c r="S17" s="27"/>
       <c r="AD17" s="22"/>
     </row>
     <row r="18" spans="2:30" ht="23">
-      <c r="B18" s="76" t="s">
+      <c r="B18" s="50" t="s">
         <v>491</v>
       </c>
-      <c r="C18" s="77"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="78"/>
-      <c r="M18" s="77"/>
-      <c r="N18" s="79"/>
-      <c r="O18" s="80"/>
-      <c r="P18" s="78"/>
-      <c r="Q18" s="78"/>
       <c r="S18" s="27"/>
       <c r="AD18" s="22"/>
     </row>
     <row r="19" spans="2:30" ht="23">
-      <c r="B19" s="76" t="s">
+      <c r="B19" s="50" t="s">
         <v>492</v>
       </c>
-      <c r="C19" s="77"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="78"/>
-      <c r="L19" s="78"/>
-      <c r="M19" s="77"/>
-      <c r="N19" s="79"/>
-      <c r="O19" s="80"/>
-      <c r="P19" s="78"/>
-      <c r="Q19" s="78"/>
       <c r="S19" s="27"/>
       <c r="AD19" s="22"/>
     </row>
     <row r="20" spans="2:30" ht="23">
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="50" t="s">
         <v>493</v>
       </c>
-      <c r="C20" s="77"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="78"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="78"/>
-      <c r="M20" s="77"/>
-      <c r="N20" s="79"/>
-      <c r="O20" s="80"/>
-      <c r="P20" s="78"/>
-      <c r="Q20" s="78"/>
       <c r="S20" s="27"/>
       <c r="AD20" s="22"/>
     </row>
     <row r="21" spans="2:30" ht="23">
-      <c r="B21" s="76" t="s">
+      <c r="B21" s="50" t="s">
         <v>494</v>
       </c>
-      <c r="C21" s="77"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="78"/>
-      <c r="K21" s="78"/>
-      <c r="L21" s="78"/>
-      <c r="M21" s="77"/>
-      <c r="N21" s="79"/>
-      <c r="O21" s="80"/>
-      <c r="P21" s="78"/>
-      <c r="Q21" s="78"/>
       <c r="S21" s="27"/>
       <c r="AD21" s="22"/>
     </row>
@@ -19841,21 +19232,6 @@
       <c r="B22" s="18" t="s">
         <v>495</v>
       </c>
-      <c r="C22" s="77"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="77"/>
-      <c r="N22" s="79"/>
-      <c r="O22" s="80"/>
-      <c r="P22" s="78"/>
-      <c r="Q22" s="78"/>
       <c r="S22" s="27"/>
       <c r="AD22" s="22"/>
     </row>
@@ -19863,149 +19239,44 @@
       <c r="B23" s="18" t="s">
         <v>496</v>
       </c>
-      <c r="C23" s="77"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="77"/>
-      <c r="N23" s="79"/>
-      <c r="O23" s="80"/>
-      <c r="P23" s="78"/>
-      <c r="Q23" s="78"/>
       <c r="S23" s="27"/>
       <c r="AD23" s="22"/>
     </row>
     <row r="24" spans="2:30" ht="23">
-      <c r="B24" s="76" t="s">
+      <c r="B24" s="50" t="s">
         <v>483</v>
       </c>
-      <c r="C24" s="77"/>
-      <c r="D24" s="78"/>
-      <c r="E24" s="77"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="78"/>
-      <c r="M24" s="77"/>
-      <c r="N24" s="79"/>
-      <c r="O24" s="80"/>
-      <c r="P24" s="78"/>
-      <c r="Q24" s="78"/>
       <c r="S24" s="27"/>
       <c r="AD24" s="22"/>
     </row>
     <row r="25" spans="2:30">
-      <c r="B25" s="80"/>
-      <c r="C25" s="77"/>
-      <c r="D25" s="78"/>
-      <c r="E25" s="77"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="78"/>
-      <c r="K25" s="78"/>
-      <c r="L25" s="78"/>
-      <c r="M25" s="77"/>
-      <c r="N25" s="79"/>
-      <c r="O25" s="80"/>
-      <c r="P25" s="78"/>
-      <c r="Q25" s="78"/>
+      <c r="B25"/>
       <c r="S25" s="27"/>
       <c r="AD25" s="22"/>
     </row>
     <row r="26" spans="2:30" ht="23">
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C26" s="77"/>
-      <c r="D26" s="78"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="78"/>
-      <c r="G26" s="77"/>
-      <c r="H26" s="78"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="78"/>
-      <c r="K26" s="78"/>
-      <c r="L26" s="78"/>
-      <c r="M26" s="77"/>
-      <c r="N26" s="79"/>
-      <c r="O26" s="80"/>
-      <c r="P26" s="78"/>
-      <c r="Q26" s="78"/>
       <c r="S26" s="27"/>
       <c r="AD26" s="22"/>
     </row>
     <row r="27" spans="2:30" ht="23">
-      <c r="B27" s="76" t="s">
+      <c r="B27" s="50" t="s">
         <v>266</v>
       </c>
-      <c r="C27" s="77"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="78"/>
-      <c r="K27" s="78"/>
-      <c r="L27" s="78"/>
-      <c r="M27" s="77"/>
-      <c r="N27" s="79"/>
-      <c r="O27" s="80"/>
-      <c r="P27" s="78"/>
-      <c r="Q27" s="78"/>
       <c r="S27" s="27"/>
       <c r="AD27" s="22"/>
     </row>
     <row r="28" spans="2:30" ht="23">
-      <c r="B28" s="76" t="s">
+      <c r="B28" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="77"/>
-      <c r="D28" s="78"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="78"/>
-      <c r="K28" s="78"/>
-      <c r="L28" s="78"/>
-      <c r="M28" s="77"/>
-      <c r="N28" s="79"/>
-      <c r="O28" s="80"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="78"/>
       <c r="S28" s="27"/>
       <c r="AD28" s="22"/>
     </row>
     <row r="29" spans="2:30">
-      <c r="B29" s="80"/>
-      <c r="C29" s="77"/>
-      <c r="D29" s="78"/>
-      <c r="E29" s="77"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="78"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="78"/>
-      <c r="K29" s="78"/>
-      <c r="L29" s="78"/>
-      <c r="M29" s="77"/>
-      <c r="N29" s="79"/>
-      <c r="O29" s="80"/>
-      <c r="P29" s="78"/>
-      <c r="Q29" s="78"/>
+      <c r="B29"/>
       <c r="S29" s="27"/>
       <c r="AD29" s="22"/>
     </row>
@@ -20013,21 +19284,6 @@
       <c r="B30" s="18" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="77"/>
-      <c r="D30" s="78"/>
-      <c r="E30" s="77"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="77"/>
-      <c r="H30" s="78"/>
-      <c r="I30" s="78"/>
-      <c r="J30" s="78"/>
-      <c r="K30" s="78"/>
-      <c r="L30" s="78"/>
-      <c r="M30" s="77"/>
-      <c r="N30" s="79"/>
-      <c r="O30" s="80"/>
-      <c r="P30" s="78"/>
-      <c r="Q30" s="78"/>
       <c r="S30" s="27"/>
       <c r="AD30" s="22"/>
     </row>
@@ -20035,21 +19291,21 @@
       <c r="B31" s="18" t="s">
         <v>498</v>
       </c>
-      <c r="C31" s="77"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="77"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="78"/>
-      <c r="K31" s="78"/>
-      <c r="L31" s="78"/>
-      <c r="M31" s="77"/>
-      <c r="N31" s="79"/>
-      <c r="O31" s="80"/>
-      <c r="P31" s="78"/>
-      <c r="Q31" s="78"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="23"/>
+      <c r="O31"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22"/>
       <c r="S31" s="31"/>
       <c r="T31" s="28"/>
       <c r="U31" s="30"/>
@@ -20060,21 +19316,21 @@
       <c r="B32" s="18" t="s">
         <v>499</v>
       </c>
-      <c r="C32" s="77"/>
-      <c r="D32" s="78"/>
-      <c r="E32" s="77"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="78"/>
-      <c r="I32" s="78"/>
-      <c r="J32" s="78"/>
-      <c r="K32" s="78"/>
-      <c r="L32" s="78"/>
-      <c r="M32" s="77"/>
-      <c r="N32" s="79"/>
-      <c r="O32" s="80"/>
-      <c r="P32" s="78"/>
-      <c r="Q32" s="78"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="23"/>
+      <c r="O32"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22"/>
       <c r="S32" s="31"/>
       <c r="T32" s="28"/>
       <c r="U32" s="30"/>
@@ -20085,21 +19341,21 @@
       <c r="B33" s="18" t="s">
         <v>500</v>
       </c>
-      <c r="C33" s="77"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="78"/>
-      <c r="K33" s="78"/>
-      <c r="L33" s="78"/>
-      <c r="M33" s="77"/>
-      <c r="N33" s="79"/>
-      <c r="O33" s="80"/>
-      <c r="P33" s="78"/>
-      <c r="Q33" s="78"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="23"/>
+      <c r="O33"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22"/>
       <c r="S33" s="31"/>
       <c r="T33" s="28"/>
       <c r="U33" s="30"/>
@@ -20107,383 +19363,131 @@
       <c r="X33" s="33"/>
     </row>
     <row r="34" spans="2:30" ht="23">
-      <c r="B34" s="76" t="s">
+      <c r="B34" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C34" s="77"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="78"/>
-      <c r="G34" s="77"/>
-      <c r="H34" s="78"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="78"/>
-      <c r="K34" s="78"/>
-      <c r="L34" s="78"/>
-      <c r="M34" s="77"/>
-      <c r="N34" s="79"/>
-      <c r="O34" s="80"/>
-      <c r="P34" s="78"/>
-      <c r="Q34" s="78"/>
       <c r="S34" s="27"/>
       <c r="AD34" s="22"/>
     </row>
     <row r="35" spans="2:30" ht="23">
-      <c r="B35" s="76" t="s">
+      <c r="B35" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="C35" s="77"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="78"/>
-      <c r="I35" s="78"/>
-      <c r="J35" s="78"/>
-      <c r="K35" s="78"/>
-      <c r="L35" s="78"/>
-      <c r="M35" s="77"/>
-      <c r="N35" s="79"/>
-      <c r="O35" s="80"/>
-      <c r="P35" s="78"/>
-      <c r="Q35" s="78"/>
       <c r="S35" s="27"/>
       <c r="AD35" s="22"/>
     </row>
     <row r="36" spans="2:30" ht="23">
-      <c r="B36" s="76" t="s">
+      <c r="B36" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C36" s="77"/>
-      <c r="D36" s="78"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="78"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="78"/>
-      <c r="J36" s="78"/>
-      <c r="K36" s="78"/>
-      <c r="L36" s="78"/>
-      <c r="M36" s="77"/>
-      <c r="N36" s="79"/>
-      <c r="O36" s="80"/>
-      <c r="P36" s="78"/>
-      <c r="Q36" s="78"/>
       <c r="S36" s="27"/>
     </row>
     <row r="37" spans="2:30" ht="23">
       <c r="B37" s="18" t="s">
         <v>501</v>
       </c>
-      <c r="C37" s="77"/>
-      <c r="D37" s="81"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="81"/>
-      <c r="I37" s="78"/>
-      <c r="J37" s="78"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="78"/>
-      <c r="M37" s="77"/>
-      <c r="N37" s="79"/>
-      <c r="O37" s="80"/>
-      <c r="P37" s="78"/>
-      <c r="Q37" s="78"/>
+      <c r="D37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="H37" s="51"/>
       <c r="S37" s="27"/>
     </row>
     <row r="38" spans="2:30" ht="23">
       <c r="B38" s="18" t="s">
         <v>502</v>
       </c>
-      <c r="C38" s="77"/>
-      <c r="D38" s="78"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="78"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="78"/>
-      <c r="I38" s="78"/>
-      <c r="J38" s="78"/>
-      <c r="K38" s="78"/>
-      <c r="L38" s="78"/>
-      <c r="M38" s="77"/>
-      <c r="N38" s="79"/>
-      <c r="O38" s="80"/>
-      <c r="P38" s="78"/>
-      <c r="Q38" s="78"/>
       <c r="S38" s="27"/>
     </row>
     <row r="39" spans="2:30" ht="23">
       <c r="B39" s="18" t="s">
         <v>503</v>
       </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="78"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="78"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="78"/>
-      <c r="I39" s="78"/>
-      <c r="J39" s="78"/>
-      <c r="K39" s="78"/>
-      <c r="L39" s="78"/>
-      <c r="M39" s="77"/>
-      <c r="N39" s="79"/>
-      <c r="O39" s="80"/>
-      <c r="P39" s="78"/>
-      <c r="Q39" s="78"/>
       <c r="S39" s="27"/>
     </row>
     <row r="40" spans="2:30" ht="23">
       <c r="B40" s="18" t="s">
         <v>504</v>
       </c>
-      <c r="C40" s="77"/>
-      <c r="D40" s="78"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="78"/>
-      <c r="K40" s="78"/>
-      <c r="L40" s="78"/>
-      <c r="M40" s="77"/>
-      <c r="N40" s="79"/>
-      <c r="O40" s="80"/>
-      <c r="P40" s="78"/>
-      <c r="Q40" s="78"/>
       <c r="S40" s="27"/>
     </row>
     <row r="41" spans="2:30" ht="23">
       <c r="B41" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C41" s="77"/>
-      <c r="D41" s="78"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="78"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="78"/>
-      <c r="I41" s="78"/>
-      <c r="J41" s="78"/>
-      <c r="K41" s="78"/>
-      <c r="L41" s="78"/>
-      <c r="M41" s="77"/>
-      <c r="N41" s="79"/>
-      <c r="O41" s="80"/>
-      <c r="P41" s="78"/>
-      <c r="Q41" s="78"/>
       <c r="S41" s="27"/>
     </row>
     <row r="42" spans="2:30" ht="23">
       <c r="B42" s="18" t="s">
         <v>505</v>
       </c>
-      <c r="C42" s="77"/>
-      <c r="D42" s="78"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="78"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="78"/>
-      <c r="I42" s="78"/>
-      <c r="J42" s="78"/>
-      <c r="K42" s="78"/>
-      <c r="L42" s="78"/>
-      <c r="M42" s="77"/>
-      <c r="N42" s="79"/>
-      <c r="O42" s="80"/>
-      <c r="P42" s="78"/>
-      <c r="Q42" s="78"/>
       <c r="S42" s="27"/>
     </row>
     <row r="43" spans="2:30" ht="23">
       <c r="B43" s="18" t="s">
         <v>506</v>
       </c>
-      <c r="C43" s="77"/>
-      <c r="D43" s="78"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="78"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="78"/>
-      <c r="I43" s="78"/>
-      <c r="J43" s="78"/>
-      <c r="K43" s="78"/>
-      <c r="L43" s="78"/>
-      <c r="M43" s="77"/>
-      <c r="N43" s="79"/>
-      <c r="O43" s="80"/>
-      <c r="P43" s="78"/>
-      <c r="Q43" s="78"/>
       <c r="S43" s="27"/>
     </row>
     <row r="44" spans="2:30" ht="23">
       <c r="B44" s="18" t="s">
         <v>507</v>
       </c>
-      <c r="C44" s="77"/>
-      <c r="D44" s="78"/>
-      <c r="E44" s="77"/>
-      <c r="F44" s="78"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="78"/>
-      <c r="I44" s="78"/>
-      <c r="J44" s="78"/>
-      <c r="K44" s="78"/>
-      <c r="L44" s="78"/>
-      <c r="M44" s="77"/>
-      <c r="N44" s="79"/>
-      <c r="O44" s="80"/>
-      <c r="P44" s="78"/>
-      <c r="Q44" s="78"/>
       <c r="S44" s="27"/>
     </row>
     <row r="45" spans="2:30" ht="23">
       <c r="B45" s="18" t="s">
         <v>508</v>
       </c>
-      <c r="C45" s="77"/>
-      <c r="D45" s="78"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="78"/>
-      <c r="G45" s="77"/>
-      <c r="H45" s="78"/>
-      <c r="I45" s="78"/>
-      <c r="J45" s="78"/>
-      <c r="K45" s="78"/>
-      <c r="L45" s="78"/>
-      <c r="M45" s="77"/>
-      <c r="N45" s="79"/>
-      <c r="O45" s="80"/>
-      <c r="P45" s="78"/>
-      <c r="Q45" s="78"/>
       <c r="S45" s="27"/>
     </row>
     <row r="46" spans="2:30" ht="23">
       <c r="B46" s="18" t="s">
         <v>509</v>
       </c>
-      <c r="C46" s="77"/>
-      <c r="D46" s="78"/>
-      <c r="E46" s="77"/>
-      <c r="F46" s="78"/>
-      <c r="G46" s="77"/>
-      <c r="H46" s="78"/>
-      <c r="I46" s="78"/>
-      <c r="J46" s="78"/>
-      <c r="K46" s="78"/>
-      <c r="L46" s="78"/>
-      <c r="M46" s="77"/>
-      <c r="N46" s="79"/>
-      <c r="O46" s="80"/>
-      <c r="P46" s="78"/>
-      <c r="Q46" s="78"/>
       <c r="S46" s="27"/>
     </row>
     <row r="47" spans="2:30" ht="23">
       <c r="B47" s="18" t="s">
         <v>510</v>
       </c>
-      <c r="C47" s="77"/>
-      <c r="D47" s="78"/>
-      <c r="E47" s="77"/>
-      <c r="F47" s="78"/>
-      <c r="G47" s="77"/>
-      <c r="H47" s="78"/>
-      <c r="I47" s="78"/>
-      <c r="J47" s="78"/>
-      <c r="K47" s="78"/>
-      <c r="L47" s="78"/>
-      <c r="M47" s="77"/>
-      <c r="N47" s="79"/>
-      <c r="O47" s="80"/>
-      <c r="P47" s="78"/>
-      <c r="Q47" s="78"/>
       <c r="S47" s="27"/>
     </row>
     <row r="48" spans="2:30" ht="23">
       <c r="B48" s="18" t="s">
         <v>511</v>
       </c>
-      <c r="C48" s="77"/>
-      <c r="D48" s="78"/>
-      <c r="E48" s="77"/>
-      <c r="F48" s="78"/>
-      <c r="G48" s="77"/>
-      <c r="H48" s="78"/>
-      <c r="I48" s="78"/>
-      <c r="J48" s="78"/>
-      <c r="K48" s="78"/>
-      <c r="L48" s="78"/>
-      <c r="M48" s="77"/>
-      <c r="N48" s="79"/>
-      <c r="O48" s="80"/>
-      <c r="P48" s="78"/>
-      <c r="Q48" s="78"/>
       <c r="S48" s="27"/>
     </row>
     <row r="49" spans="2:30" ht="23">
       <c r="B49" s="18" t="s">
         <v>512</v>
       </c>
-      <c r="C49" s="77"/>
-      <c r="D49" s="78"/>
-      <c r="E49" s="77"/>
-      <c r="F49" s="78"/>
-      <c r="G49" s="77"/>
-      <c r="H49" s="78"/>
-      <c r="I49" s="78"/>
-      <c r="J49" s="78"/>
-      <c r="K49" s="78"/>
-      <c r="L49" s="78"/>
-      <c r="M49" s="77"/>
-      <c r="N49" s="79"/>
-      <c r="O49" s="80"/>
-      <c r="P49" s="78"/>
-      <c r="Q49" s="78"/>
       <c r="S49" s="27"/>
     </row>
     <row r="50" spans="2:30" ht="23">
       <c r="B50" s="18" t="s">
         <v>513</v>
       </c>
-      <c r="C50" s="77"/>
-      <c r="D50" s="78"/>
-      <c r="E50" s="77"/>
-      <c r="F50" s="78"/>
-      <c r="G50" s="77"/>
-      <c r="H50" s="78"/>
-      <c r="I50" s="78"/>
-      <c r="J50" s="78"/>
-      <c r="K50" s="78"/>
-      <c r="L50" s="78"/>
-      <c r="M50" s="77"/>
-      <c r="N50" s="79"/>
-      <c r="O50" s="80"/>
-      <c r="P50" s="78"/>
-      <c r="Q50" s="78"/>
       <c r="S50" s="27"/>
     </row>
     <row r="51" spans="2:30" s="29" customFormat="1" ht="23">
-      <c r="B51" s="76" t="s">
+      <c r="B51" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C51" s="77"/>
-      <c r="D51" s="78"/>
-      <c r="E51" s="77"/>
-      <c r="F51" s="78"/>
-      <c r="G51" s="77"/>
-      <c r="H51" s="78"/>
-      <c r="I51" s="78"/>
-      <c r="J51" s="78"/>
-      <c r="K51" s="78"/>
-      <c r="L51" s="78"/>
-      <c r="M51" s="77"/>
-      <c r="N51" s="79"/>
-      <c r="O51" s="80"/>
-      <c r="P51" s="78"/>
-      <c r="Q51" s="78"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="22"/>
+      <c r="J51" s="22"/>
+      <c r="K51" s="22"/>
+      <c r="L51" s="22"/>
+      <c r="M51" s="21"/>
+      <c r="N51" s="23"/>
+      <c r="O51"/>
+      <c r="P51" s="22"/>
+      <c r="Q51" s="22"/>
       <c r="S51" s="31"/>
       <c r="T51" s="28"/>
       <c r="U51" s="30"/>
@@ -20492,24 +19496,24 @@
       <c r="AD51" s="20"/>
     </row>
     <row r="52" spans="2:30" s="29" customFormat="1" ht="23">
-      <c r="B52" s="76" t="s">
+      <c r="B52" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C52" s="77"/>
-      <c r="D52" s="78"/>
-      <c r="E52" s="77"/>
-      <c r="F52" s="78"/>
-      <c r="G52" s="77"/>
-      <c r="H52" s="78"/>
-      <c r="I52" s="78"/>
-      <c r="J52" s="78"/>
-      <c r="K52" s="78"/>
-      <c r="L52" s="78"/>
-      <c r="M52" s="77"/>
-      <c r="N52" s="79"/>
-      <c r="O52" s="80"/>
-      <c r="P52" s="78"/>
-      <c r="Q52" s="78"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="22"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="21"/>
+      <c r="N52" s="23"/>
+      <c r="O52"/>
+      <c r="P52" s="22"/>
+      <c r="Q52" s="22"/>
       <c r="S52" s="31"/>
       <c r="T52" s="28"/>
       <c r="U52" s="30"/>
@@ -20518,24 +19522,24 @@
       <c r="AD52" s="20"/>
     </row>
     <row r="53" spans="2:30" s="29" customFormat="1" ht="23">
-      <c r="B53" s="76" t="s">
+      <c r="B53" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C53" s="77"/>
-      <c r="D53" s="78"/>
-      <c r="E53" s="77"/>
-      <c r="F53" s="78"/>
-      <c r="G53" s="77"/>
-      <c r="H53" s="78"/>
-      <c r="I53" s="78"/>
-      <c r="J53" s="78"/>
-      <c r="K53" s="78"/>
-      <c r="L53" s="78"/>
-      <c r="M53" s="77"/>
-      <c r="N53" s="79"/>
-      <c r="O53" s="80"/>
-      <c r="P53" s="78"/>
-      <c r="Q53" s="78"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="22"/>
+      <c r="K53" s="22"/>
+      <c r="L53" s="22"/>
+      <c r="M53" s="21"/>
+      <c r="N53" s="23"/>
+      <c r="O53"/>
+      <c r="P53" s="22"/>
+      <c r="Q53" s="22"/>
       <c r="S53" s="31"/>
       <c r="T53" s="28"/>
       <c r="U53" s="30"/>
@@ -20547,546 +19551,171 @@
       <c r="B54" s="18" t="s">
         <v>514</v>
       </c>
-      <c r="C54" s="77"/>
-      <c r="D54" s="78"/>
-      <c r="E54" s="77"/>
-      <c r="F54" s="78"/>
-      <c r="G54" s="77"/>
-      <c r="H54" s="78"/>
-      <c r="I54" s="78"/>
-      <c r="J54" s="78"/>
-      <c r="K54" s="78"/>
-      <c r="L54" s="78"/>
-      <c r="M54" s="77"/>
-      <c r="N54" s="79"/>
-      <c r="O54" s="80"/>
-      <c r="P54" s="78"/>
-      <c r="Q54" s="78"/>
       <c r="S54" s="27"/>
     </row>
     <row r="55" spans="2:30" ht="23">
       <c r="B55" s="18" t="s">
         <v>515</v>
       </c>
-      <c r="C55" s="77"/>
-      <c r="D55" s="78"/>
-      <c r="E55" s="77"/>
-      <c r="F55" s="78"/>
-      <c r="G55" s="77"/>
-      <c r="H55" s="78"/>
-      <c r="I55" s="78"/>
-      <c r="J55" s="78"/>
-      <c r="K55" s="78"/>
-      <c r="L55" s="78"/>
-      <c r="M55" s="77"/>
-      <c r="N55" s="79"/>
-      <c r="O55" s="80"/>
-      <c r="P55" s="78"/>
-      <c r="Q55" s="78"/>
       <c r="S55" s="27"/>
     </row>
     <row r="56" spans="2:30" ht="23">
       <c r="B56" s="18" t="s">
         <v>516</v>
       </c>
-      <c r="C56" s="77"/>
-      <c r="D56" s="78"/>
-      <c r="E56" s="77"/>
-      <c r="F56" s="78"/>
-      <c r="G56" s="77"/>
-      <c r="H56" s="78"/>
-      <c r="I56" s="78"/>
-      <c r="J56" s="78"/>
-      <c r="K56" s="78"/>
-      <c r="L56" s="78"/>
-      <c r="M56" s="77"/>
-      <c r="N56" s="79"/>
-      <c r="O56" s="80"/>
-      <c r="P56" s="78"/>
-      <c r="Q56" s="78"/>
       <c r="S56" s="27"/>
     </row>
     <row r="57" spans="2:30" ht="23">
       <c r="B57" s="18" t="s">
         <v>517</v>
       </c>
-      <c r="C57" s="77"/>
-      <c r="D57" s="78"/>
-      <c r="E57" s="77"/>
-      <c r="F57" s="78"/>
-      <c r="G57" s="77"/>
-      <c r="H57" s="78"/>
-      <c r="I57" s="78"/>
-      <c r="J57" s="78"/>
-      <c r="K57" s="78"/>
-      <c r="L57" s="78"/>
-      <c r="M57" s="77"/>
-      <c r="N57" s="79"/>
-      <c r="O57" s="80"/>
-      <c r="P57" s="78"/>
-      <c r="Q57" s="78"/>
       <c r="S57" s="27"/>
     </row>
     <row r="58" spans="2:30" ht="23">
       <c r="B58" s="18" t="s">
         <v>518</v>
       </c>
-      <c r="C58" s="77"/>
-      <c r="D58" s="78"/>
-      <c r="E58" s="77"/>
-      <c r="F58" s="78"/>
-      <c r="G58" s="77"/>
-      <c r="H58" s="78"/>
-      <c r="I58" s="78"/>
-      <c r="J58" s="78"/>
-      <c r="K58" s="78"/>
-      <c r="L58" s="78"/>
-      <c r="M58" s="77"/>
-      <c r="N58" s="79"/>
-      <c r="O58" s="80"/>
-      <c r="P58" s="78"/>
-      <c r="Q58" s="78"/>
       <c r="S58" s="27"/>
     </row>
     <row r="59" spans="2:30" ht="23">
       <c r="B59" s="18" t="s">
         <v>519</v>
       </c>
-      <c r="C59" s="77"/>
-      <c r="D59" s="78"/>
-      <c r="E59" s="77"/>
-      <c r="F59" s="78"/>
-      <c r="G59" s="77"/>
-      <c r="H59" s="78"/>
-      <c r="I59" s="78"/>
-      <c r="J59" s="78"/>
-      <c r="K59" s="78"/>
-      <c r="L59" s="78"/>
-      <c r="M59" s="77"/>
-      <c r="N59" s="79"/>
-      <c r="O59" s="80"/>
-      <c r="P59" s="78"/>
-      <c r="Q59" s="78"/>
       <c r="S59" s="27"/>
     </row>
     <row r="60" spans="2:30" ht="23">
       <c r="B60" s="18" t="s">
         <v>520</v>
       </c>
-      <c r="C60" s="77"/>
-      <c r="D60" s="78"/>
-      <c r="E60" s="77"/>
-      <c r="F60" s="78"/>
-      <c r="G60" s="77"/>
-      <c r="H60" s="78"/>
-      <c r="I60" s="78"/>
-      <c r="J60" s="78"/>
-      <c r="K60" s="78"/>
-      <c r="L60" s="78"/>
-      <c r="M60" s="77"/>
-      <c r="N60" s="79"/>
-      <c r="O60" s="80"/>
-      <c r="P60" s="78"/>
-      <c r="Q60" s="78"/>
       <c r="S60" s="27"/>
     </row>
     <row r="61" spans="2:30" ht="23">
       <c r="B61" s="18" t="s">
         <v>521</v>
       </c>
-      <c r="C61" s="77"/>
-      <c r="D61" s="78"/>
-      <c r="E61" s="77"/>
-      <c r="F61" s="78"/>
-      <c r="G61" s="77"/>
-      <c r="H61" s="78"/>
-      <c r="I61" s="78"/>
-      <c r="J61" s="78"/>
-      <c r="K61" s="78"/>
-      <c r="L61" s="78"/>
-      <c r="M61" s="77"/>
-      <c r="N61" s="79"/>
-      <c r="O61" s="80"/>
-      <c r="P61" s="78"/>
-      <c r="Q61" s="78"/>
       <c r="S61" s="27"/>
     </row>
     <row r="62" spans="2:30" ht="23">
       <c r="B62" s="18" t="s">
         <v>522</v>
       </c>
-      <c r="C62" s="77"/>
-      <c r="D62" s="78"/>
-      <c r="E62" s="77"/>
-      <c r="F62" s="78"/>
-      <c r="G62" s="77"/>
-      <c r="H62" s="78"/>
-      <c r="I62" s="78"/>
-      <c r="J62" s="78"/>
-      <c r="K62" s="78"/>
-      <c r="L62" s="78"/>
-      <c r="M62" s="77"/>
-      <c r="N62" s="79"/>
-      <c r="O62" s="80"/>
-      <c r="P62" s="78"/>
-      <c r="Q62" s="78"/>
       <c r="S62" s="27"/>
     </row>
     <row r="63" spans="2:30" ht="23">
       <c r="B63" s="18" t="s">
         <v>523</v>
       </c>
-      <c r="C63" s="77"/>
-      <c r="D63" s="78"/>
-      <c r="E63" s="77"/>
-      <c r="F63" s="78"/>
-      <c r="G63" s="77"/>
-      <c r="H63" s="78"/>
-      <c r="I63" s="78"/>
-      <c r="J63" s="78"/>
-      <c r="K63" s="78"/>
-      <c r="L63" s="78"/>
-      <c r="M63" s="77"/>
-      <c r="N63" s="79"/>
-      <c r="O63" s="80"/>
-      <c r="P63" s="78"/>
-      <c r="Q63" s="78"/>
       <c r="S63" s="27"/>
     </row>
     <row r="64" spans="2:30" ht="23">
       <c r="B64" s="18" t="s">
         <v>524</v>
       </c>
-      <c r="C64" s="77"/>
-      <c r="D64" s="78"/>
-      <c r="E64" s="77"/>
-      <c r="F64" s="78"/>
-      <c r="G64" s="77"/>
-      <c r="H64" s="78"/>
-      <c r="I64" s="78"/>
-      <c r="J64" s="78"/>
-      <c r="K64" s="78"/>
-      <c r="L64" s="78"/>
-      <c r="M64" s="77"/>
-      <c r="N64" s="79"/>
-      <c r="O64" s="80"/>
-      <c r="P64" s="78"/>
-      <c r="Q64" s="78"/>
       <c r="S64" s="27"/>
     </row>
     <row r="65" spans="2:30" ht="23">
       <c r="B65" s="18" t="s">
         <v>525</v>
       </c>
-      <c r="C65" s="77"/>
-      <c r="D65" s="78"/>
-      <c r="E65" s="77"/>
-      <c r="F65" s="78"/>
-      <c r="G65" s="77"/>
-      <c r="H65" s="78"/>
-      <c r="I65" s="78"/>
-      <c r="J65" s="78"/>
-      <c r="K65" s="78"/>
-      <c r="L65" s="78"/>
-      <c r="M65" s="77"/>
-      <c r="N65" s="79"/>
-      <c r="O65" s="80"/>
-      <c r="P65" s="78"/>
-      <c r="Q65" s="78"/>
       <c r="S65" s="27"/>
     </row>
     <row r="66" spans="2:30" ht="23">
       <c r="B66" s="18" t="s">
         <v>526</v>
       </c>
-      <c r="C66" s="77"/>
-      <c r="D66" s="78"/>
-      <c r="E66" s="77"/>
-      <c r="F66" s="78"/>
-      <c r="G66" s="77"/>
-      <c r="H66" s="78"/>
-      <c r="I66" s="78"/>
-      <c r="J66" s="78"/>
-      <c r="K66" s="78"/>
-      <c r="L66" s="78"/>
-      <c r="M66" s="77"/>
-      <c r="N66" s="79"/>
-      <c r="O66" s="80"/>
-      <c r="P66" s="78"/>
-      <c r="Q66" s="78"/>
       <c r="S66" s="27"/>
     </row>
     <row r="67" spans="2:30" ht="23">
       <c r="B67" s="18" t="s">
         <v>527</v>
       </c>
-      <c r="C67" s="77"/>
-      <c r="D67" s="78"/>
-      <c r="E67" s="77"/>
-      <c r="F67" s="78"/>
-      <c r="G67" s="77"/>
-      <c r="H67" s="78"/>
-      <c r="I67" s="78"/>
-      <c r="J67" s="78"/>
-      <c r="K67" s="78"/>
-      <c r="L67" s="78"/>
-      <c r="M67" s="77"/>
-      <c r="N67" s="79"/>
-      <c r="O67" s="80"/>
-      <c r="P67" s="78"/>
-      <c r="Q67" s="78"/>
       <c r="S67" s="27"/>
     </row>
     <row r="68" spans="2:30" ht="23">
       <c r="B68" s="18" t="s">
         <v>528</v>
       </c>
-      <c r="C68" s="77"/>
-      <c r="D68" s="78"/>
-      <c r="E68" s="77"/>
-      <c r="F68" s="78"/>
-      <c r="G68" s="77"/>
-      <c r="H68" s="78"/>
-      <c r="I68" s="78"/>
-      <c r="J68" s="78"/>
-      <c r="K68" s="78"/>
-      <c r="L68" s="78"/>
-      <c r="M68" s="77"/>
-      <c r="N68" s="79"/>
-      <c r="O68" s="80"/>
-      <c r="P68" s="78"/>
-      <c r="Q68" s="78"/>
       <c r="S68" s="27"/>
     </row>
     <row r="69" spans="2:30" ht="23">
       <c r="B69" s="18" t="s">
         <v>529</v>
       </c>
-      <c r="C69" s="77"/>
-      <c r="D69" s="78"/>
-      <c r="E69" s="77"/>
-      <c r="F69" s="78"/>
-      <c r="G69" s="77"/>
-      <c r="H69" s="78"/>
-      <c r="I69" s="78"/>
-      <c r="J69" s="78"/>
-      <c r="K69" s="78"/>
-      <c r="L69" s="78"/>
-      <c r="M69" s="77"/>
-      <c r="N69" s="79"/>
-      <c r="O69" s="80"/>
-      <c r="P69" s="78"/>
-      <c r="Q69" s="78"/>
       <c r="S69" s="27"/>
     </row>
     <row r="70" spans="2:30" ht="23">
       <c r="B70" s="18" t="s">
         <v>530</v>
       </c>
-      <c r="C70" s="77"/>
-      <c r="D70" s="78"/>
-      <c r="E70" s="77"/>
-      <c r="F70" s="78"/>
-      <c r="G70" s="77"/>
-      <c r="H70" s="78"/>
-      <c r="I70" s="78"/>
-      <c r="J70" s="78"/>
-      <c r="K70" s="78"/>
-      <c r="L70" s="78"/>
-      <c r="M70" s="77"/>
-      <c r="N70" s="79"/>
-      <c r="O70" s="80"/>
-      <c r="P70" s="78"/>
-      <c r="Q70" s="78"/>
       <c r="S70" s="27"/>
     </row>
     <row r="71" spans="2:30" ht="23">
       <c r="B71" s="18" t="s">
         <v>531</v>
       </c>
-      <c r="C71" s="77"/>
-      <c r="D71" s="78"/>
-      <c r="E71" s="77"/>
-      <c r="F71" s="78"/>
-      <c r="G71" s="77"/>
-      <c r="H71" s="78"/>
-      <c r="I71" s="78"/>
-      <c r="J71" s="78"/>
-      <c r="K71" s="78"/>
-      <c r="L71" s="78"/>
-      <c r="M71" s="77"/>
-      <c r="N71" s="79"/>
-      <c r="O71" s="80"/>
-      <c r="P71" s="78"/>
-      <c r="Q71" s="78"/>
       <c r="S71" s="27"/>
     </row>
     <row r="72" spans="2:30" ht="23">
       <c r="B72" s="18" t="s">
         <v>532</v>
       </c>
-      <c r="C72" s="77"/>
-      <c r="D72" s="78"/>
-      <c r="E72" s="77"/>
-      <c r="F72" s="78"/>
-      <c r="G72" s="77"/>
-      <c r="H72" s="78"/>
-      <c r="I72" s="78"/>
-      <c r="J72" s="78"/>
-      <c r="K72" s="78"/>
-      <c r="L72" s="78"/>
-      <c r="M72" s="77"/>
-      <c r="N72" s="79"/>
-      <c r="O72" s="80"/>
-      <c r="P72" s="78"/>
-      <c r="Q72" s="78"/>
       <c r="S72" s="27"/>
     </row>
     <row r="73" spans="2:30" ht="23">
       <c r="B73" s="18" t="s">
         <v>533</v>
       </c>
-      <c r="C73" s="77"/>
-      <c r="D73" s="78"/>
-      <c r="E73" s="77"/>
-      <c r="F73" s="78"/>
-      <c r="G73" s="77"/>
-      <c r="H73" s="78"/>
-      <c r="I73" s="78"/>
-      <c r="J73" s="78"/>
-      <c r="K73" s="78"/>
-      <c r="L73" s="78"/>
-      <c r="M73" s="77"/>
-      <c r="N73" s="79"/>
-      <c r="O73" s="80"/>
-      <c r="P73" s="78"/>
-      <c r="Q73" s="78"/>
       <c r="S73" s="27"/>
     </row>
     <row r="74" spans="2:30" ht="23">
       <c r="B74" s="18" t="s">
         <v>534</v>
       </c>
-      <c r="C74" s="77"/>
-      <c r="D74" s="78"/>
-      <c r="E74" s="77"/>
-      <c r="F74" s="78"/>
-      <c r="G74" s="77"/>
-      <c r="H74" s="78"/>
-      <c r="I74" s="78"/>
-      <c r="J74" s="78"/>
-      <c r="K74" s="78"/>
-      <c r="L74" s="78"/>
-      <c r="M74" s="77"/>
-      <c r="N74" s="79"/>
-      <c r="O74" s="80"/>
-      <c r="P74" s="78"/>
-      <c r="Q74" s="78"/>
       <c r="S74" s="27"/>
     </row>
     <row r="75" spans="2:30" ht="23">
       <c r="B75" s="18" t="s">
         <v>535</v>
       </c>
-      <c r="C75" s="77"/>
-      <c r="D75" s="78"/>
-      <c r="E75" s="77"/>
-      <c r="F75" s="78"/>
-      <c r="G75" s="77"/>
-      <c r="H75" s="78"/>
-      <c r="I75" s="78"/>
-      <c r="J75" s="78"/>
-      <c r="K75" s="78"/>
-      <c r="L75" s="78"/>
-      <c r="M75" s="77"/>
-      <c r="N75" s="79"/>
-      <c r="O75" s="80"/>
-      <c r="P75" s="78"/>
-      <c r="Q75" s="78"/>
       <c r="S75" s="27"/>
     </row>
     <row r="76" spans="2:30" ht="23">
-      <c r="B76" s="76" t="s">
+      <c r="B76" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C76" s="77"/>
-      <c r="D76" s="78"/>
-      <c r="E76" s="77"/>
-      <c r="F76" s="78"/>
-      <c r="G76" s="77"/>
-      <c r="H76" s="78"/>
-      <c r="I76" s="78"/>
-      <c r="J76" s="78"/>
-      <c r="K76" s="78"/>
-      <c r="L76" s="78"/>
-      <c r="M76" s="77"/>
-      <c r="N76" s="79"/>
-      <c r="O76" s="80"/>
-      <c r="P76" s="78"/>
-      <c r="Q76" s="78"/>
       <c r="S76" s="27"/>
     </row>
     <row r="77" spans="2:30" ht="23">
-      <c r="B77" s="76" t="s">
+      <c r="B77" s="50" t="s">
         <v>143</v>
       </c>
-      <c r="C77" s="77"/>
-      <c r="D77" s="78"/>
-      <c r="E77" s="77"/>
-      <c r="F77" s="78"/>
-      <c r="G77" s="77"/>
-      <c r="H77" s="78"/>
-      <c r="I77" s="78"/>
-      <c r="J77" s="78"/>
-      <c r="K77" s="78"/>
-      <c r="L77" s="78"/>
-      <c r="M77" s="77"/>
-      <c r="N77" s="79"/>
-      <c r="O77" s="80"/>
-      <c r="P77" s="78"/>
-      <c r="Q77" s="78"/>
       <c r="S77" s="27"/>
     </row>
     <row r="78" spans="2:30" ht="23">
-      <c r="B78" s="76" t="s">
+      <c r="B78" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C78" s="77"/>
-      <c r="D78" s="78"/>
-      <c r="E78" s="77"/>
-      <c r="F78" s="78"/>
-      <c r="G78" s="77"/>
-      <c r="H78" s="78"/>
-      <c r="I78" s="78"/>
-      <c r="J78" s="78"/>
-      <c r="K78" s="78"/>
-      <c r="L78" s="78"/>
-      <c r="M78" s="77"/>
-      <c r="N78" s="79"/>
-      <c r="O78" s="80"/>
-      <c r="P78" s="78"/>
-      <c r="Q78" s="78"/>
       <c r="S78" s="27"/>
     </row>
     <row r="79" spans="2:30" s="29" customFormat="1" ht="23">
       <c r="B79" s="18" t="s">
         <v>536</v>
       </c>
-      <c r="C79" s="77"/>
-      <c r="D79" s="78"/>
-      <c r="E79" s="77"/>
-      <c r="F79" s="78"/>
-      <c r="G79" s="77"/>
-      <c r="H79" s="78"/>
-      <c r="I79" s="78"/>
-      <c r="J79" s="78"/>
-      <c r="K79" s="78"/>
-      <c r="L79" s="78"/>
-      <c r="M79" s="77"/>
-      <c r="N79" s="79"/>
-      <c r="O79" s="80"/>
-      <c r="P79" s="78"/>
-      <c r="Q79" s="78"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="21"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="21"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="22"/>
+      <c r="K79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="21"/>
+      <c r="N79" s="23"/>
+      <c r="O79"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
       <c r="S79" s="34"/>
       <c r="T79" s="28"/>
       <c r="U79" s="30"/>
@@ -21098,21 +19727,21 @@
       <c r="B80" s="18" t="s">
         <v>537</v>
       </c>
-      <c r="C80" s="77"/>
-      <c r="D80" s="78"/>
-      <c r="E80" s="77"/>
-      <c r="F80" s="78"/>
-      <c r="G80" s="77"/>
-      <c r="H80" s="78"/>
-      <c r="I80" s="78"/>
-      <c r="J80" s="78"/>
-      <c r="K80" s="78"/>
-      <c r="L80" s="78"/>
-      <c r="M80" s="77"/>
-      <c r="N80" s="79"/>
-      <c r="O80" s="80"/>
-      <c r="P80" s="78"/>
-      <c r="Q80" s="78"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="22"/>
+      <c r="G80" s="21"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="22"/>
+      <c r="J80" s="22"/>
+      <c r="K80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="21"/>
+      <c r="N80" s="23"/>
+      <c r="O80"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
       <c r="S80" s="34"/>
       <c r="T80" s="28"/>
       <c r="U80" s="30"/>
@@ -21124,21 +19753,21 @@
       <c r="B81" s="18" t="s">
         <v>538</v>
       </c>
-      <c r="C81" s="77"/>
-      <c r="D81" s="78"/>
-      <c r="E81" s="77"/>
-      <c r="F81" s="78"/>
-      <c r="G81" s="77"/>
-      <c r="H81" s="78"/>
-      <c r="I81" s="78"/>
-      <c r="J81" s="78"/>
-      <c r="K81" s="78"/>
-      <c r="L81" s="78"/>
-      <c r="M81" s="77"/>
-      <c r="N81" s="79"/>
-      <c r="O81" s="80"/>
-      <c r="P81" s="78"/>
-      <c r="Q81" s="78"/>
+      <c r="C81" s="21"/>
+      <c r="D81" s="22"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="21"/>
+      <c r="H81" s="22"/>
+      <c r="I81" s="22"/>
+      <c r="J81" s="22"/>
+      <c r="K81" s="22"/>
+      <c r="L81" s="22"/>
+      <c r="M81" s="21"/>
+      <c r="N81" s="23"/>
+      <c r="O81"/>
+      <c r="P81" s="22"/>
+      <c r="Q81" s="22"/>
       <c r="S81" s="34"/>
       <c r="T81" s="28"/>
       <c r="U81" s="30"/>
@@ -21150,747 +19779,201 @@
       <c r="B82" s="18" t="s">
         <v>539</v>
       </c>
-      <c r="C82" s="77"/>
-      <c r="D82" s="78"/>
-      <c r="E82" s="77"/>
-      <c r="F82" s="78"/>
-      <c r="G82" s="77"/>
-      <c r="H82" s="78"/>
-      <c r="I82" s="78"/>
-      <c r="J82" s="78"/>
-      <c r="K82" s="78"/>
-      <c r="L82" s="78"/>
-      <c r="M82" s="77"/>
-      <c r="N82" s="79"/>
-      <c r="O82" s="80"/>
-      <c r="P82" s="78"/>
-      <c r="Q82" s="78"/>
     </row>
     <row r="83" spans="2:30" ht="23">
       <c r="B83" s="18" t="s">
         <v>540</v>
       </c>
-      <c r="C83" s="77"/>
-      <c r="D83" s="78"/>
-      <c r="E83" s="77"/>
-      <c r="F83" s="78"/>
-      <c r="G83" s="77"/>
-      <c r="H83" s="78"/>
-      <c r="I83" s="78"/>
-      <c r="J83" s="78"/>
-      <c r="K83" s="78"/>
-      <c r="L83" s="78"/>
-      <c r="M83" s="77"/>
-      <c r="N83" s="79"/>
-      <c r="O83" s="80"/>
-      <c r="P83" s="78"/>
-      <c r="Q83" s="78"/>
     </row>
     <row r="84" spans="2:30" ht="23">
       <c r="B84" s="18" t="s">
         <v>541</v>
       </c>
-      <c r="C84" s="77"/>
-      <c r="D84" s="78"/>
-      <c r="E84" s="77"/>
-      <c r="F84" s="78"/>
-      <c r="G84" s="77"/>
-      <c r="H84" s="78"/>
-      <c r="I84" s="78"/>
-      <c r="J84" s="78"/>
-      <c r="K84" s="78"/>
-      <c r="L84" s="78"/>
-      <c r="M84" s="77"/>
-      <c r="N84" s="79"/>
-      <c r="O84" s="80"/>
-      <c r="P84" s="78"/>
-      <c r="Q84" s="78"/>
     </row>
     <row r="85" spans="2:30" ht="23">
       <c r="B85" s="18" t="s">
         <v>542</v>
       </c>
-      <c r="C85" s="77"/>
-      <c r="D85" s="78"/>
-      <c r="E85" s="77"/>
-      <c r="F85" s="78"/>
-      <c r="G85" s="77"/>
-      <c r="H85" s="78"/>
-      <c r="I85" s="78"/>
-      <c r="J85" s="78"/>
-      <c r="K85" s="78"/>
-      <c r="L85" s="78"/>
-      <c r="M85" s="77"/>
-      <c r="N85" s="79"/>
-      <c r="O85" s="80"/>
-      <c r="P85" s="78"/>
-      <c r="Q85" s="78"/>
     </row>
     <row r="86" spans="2:30" ht="23">
       <c r="B86" s="18" t="s">
         <v>543</v>
       </c>
-      <c r="C86" s="77"/>
-      <c r="D86" s="78"/>
-      <c r="E86" s="77"/>
-      <c r="F86" s="78"/>
-      <c r="G86" s="77"/>
-      <c r="H86" s="78"/>
-      <c r="I86" s="78"/>
-      <c r="J86" s="78"/>
-      <c r="K86" s="78"/>
-      <c r="L86" s="78"/>
-      <c r="M86" s="77"/>
-      <c r="N86" s="79"/>
-      <c r="O86" s="80"/>
-      <c r="P86" s="78"/>
-      <c r="Q86" s="78"/>
     </row>
     <row r="87" spans="2:30" ht="23">
       <c r="B87" s="18" t="s">
         <v>544</v>
       </c>
-      <c r="C87" s="77"/>
-      <c r="D87" s="78"/>
-      <c r="E87" s="77"/>
-      <c r="F87" s="78"/>
-      <c r="G87" s="77"/>
-      <c r="H87" s="78"/>
-      <c r="I87" s="78"/>
-      <c r="J87" s="78"/>
-      <c r="K87" s="78"/>
-      <c r="L87" s="78"/>
-      <c r="M87" s="77"/>
-      <c r="N87" s="79"/>
-      <c r="O87" s="80"/>
-      <c r="P87" s="78"/>
-      <c r="Q87" s="78"/>
     </row>
     <row r="88" spans="2:30" ht="23">
       <c r="B88" s="18" t="s">
         <v>545</v>
       </c>
-      <c r="C88" s="77"/>
-      <c r="D88" s="78"/>
-      <c r="E88" s="77"/>
-      <c r="F88" s="78"/>
-      <c r="G88" s="77"/>
-      <c r="H88" s="78"/>
-      <c r="I88" s="78"/>
-      <c r="J88" s="78"/>
-      <c r="K88" s="78"/>
-      <c r="L88" s="78"/>
-      <c r="M88" s="77"/>
-      <c r="N88" s="79"/>
-      <c r="O88" s="80"/>
-      <c r="P88" s="78"/>
-      <c r="Q88" s="78"/>
     </row>
     <row r="89" spans="2:30" ht="23">
       <c r="B89" s="18" t="s">
         <v>546</v>
       </c>
-      <c r="C89" s="77"/>
-      <c r="D89" s="78"/>
-      <c r="E89" s="77"/>
-      <c r="F89" s="78"/>
-      <c r="G89" s="77"/>
-      <c r="H89" s="78"/>
-      <c r="I89" s="78"/>
-      <c r="J89" s="78"/>
-      <c r="K89" s="78"/>
-      <c r="L89" s="78"/>
-      <c r="M89" s="77"/>
-      <c r="N89" s="79"/>
-      <c r="O89" s="80"/>
-      <c r="P89" s="78"/>
-      <c r="Q89" s="78"/>
     </row>
     <row r="90" spans="2:30" ht="23">
       <c r="B90" s="18" t="s">
         <v>547</v>
       </c>
-      <c r="C90" s="77"/>
-      <c r="D90" s="78"/>
-      <c r="E90" s="77"/>
-      <c r="F90" s="78"/>
-      <c r="G90" s="77"/>
-      <c r="H90" s="78"/>
-      <c r="I90" s="78"/>
-      <c r="J90" s="78"/>
-      <c r="K90" s="78"/>
-      <c r="L90" s="78"/>
-      <c r="M90" s="77"/>
-      <c r="N90" s="79"/>
-      <c r="O90" s="80"/>
-      <c r="P90" s="78"/>
-      <c r="Q90" s="78"/>
     </row>
     <row r="91" spans="2:30" ht="23">
       <c r="B91" s="18" t="s">
         <v>548</v>
       </c>
-      <c r="C91" s="77"/>
-      <c r="D91" s="78"/>
-      <c r="E91" s="77"/>
-      <c r="F91" s="78"/>
-      <c r="G91" s="77"/>
-      <c r="H91" s="78"/>
-      <c r="I91" s="78"/>
-      <c r="J91" s="78"/>
-      <c r="K91" s="78"/>
-      <c r="L91" s="78"/>
-      <c r="M91" s="77"/>
-      <c r="N91" s="79"/>
-      <c r="O91" s="80"/>
-      <c r="P91" s="78"/>
-      <c r="Q91" s="78"/>
     </row>
     <row r="92" spans="2:30" ht="23">
       <c r="B92" s="18" t="s">
         <v>549</v>
       </c>
-      <c r="C92" s="77"/>
-      <c r="D92" s="78"/>
-      <c r="E92" s="77"/>
-      <c r="F92" s="78"/>
-      <c r="G92" s="77"/>
-      <c r="H92" s="78"/>
-      <c r="I92" s="78"/>
-      <c r="J92" s="78"/>
-      <c r="K92" s="78"/>
-      <c r="L92" s="78"/>
-      <c r="M92" s="77"/>
-      <c r="N92" s="79"/>
-      <c r="O92" s="80"/>
-      <c r="P92" s="78"/>
-      <c r="Q92" s="78"/>
     </row>
     <row r="93" spans="2:30" ht="23">
       <c r="B93" s="18" t="s">
         <v>550</v>
       </c>
-      <c r="C93" s="77"/>
-      <c r="D93" s="78"/>
-      <c r="E93" s="77"/>
-      <c r="F93" s="78"/>
-      <c r="G93" s="77"/>
-      <c r="H93" s="78"/>
-      <c r="I93" s="78"/>
-      <c r="J93" s="78"/>
-      <c r="K93" s="78"/>
-      <c r="L93" s="78"/>
-      <c r="M93" s="77"/>
-      <c r="N93" s="79"/>
-      <c r="O93" s="80"/>
-      <c r="P93" s="78"/>
-      <c r="Q93" s="78"/>
     </row>
     <row r="94" spans="2:30" ht="23">
       <c r="B94" s="18" t="s">
         <v>551</v>
       </c>
-      <c r="C94" s="77"/>
-      <c r="D94" s="78"/>
-      <c r="E94" s="77"/>
-      <c r="F94" s="78"/>
-      <c r="G94" s="77"/>
-      <c r="H94" s="78"/>
-      <c r="I94" s="78"/>
-      <c r="J94" s="78"/>
-      <c r="K94" s="78"/>
-      <c r="L94" s="78"/>
-      <c r="M94" s="77"/>
-      <c r="N94" s="79"/>
-      <c r="O94" s="80"/>
-      <c r="P94" s="78"/>
-      <c r="Q94" s="78"/>
     </row>
     <row r="95" spans="2:30" ht="23">
       <c r="B95" s="18" t="s">
         <v>552</v>
       </c>
-      <c r="C95" s="77"/>
-      <c r="D95" s="78"/>
-      <c r="E95" s="77"/>
-      <c r="F95" s="78"/>
-      <c r="G95" s="77"/>
-      <c r="H95" s="78"/>
-      <c r="I95" s="78"/>
-      <c r="J95" s="78"/>
-      <c r="K95" s="78"/>
-      <c r="L95" s="78"/>
-      <c r="M95" s="77"/>
-      <c r="N95" s="79"/>
-      <c r="O95" s="80"/>
-      <c r="P95" s="78"/>
-      <c r="Q95" s="78"/>
     </row>
     <row r="96" spans="2:30" ht="23">
       <c r="B96" s="18" t="s">
         <v>553</v>
       </c>
-      <c r="C96" s="77"/>
-      <c r="D96" s="78"/>
-      <c r="E96" s="77"/>
-      <c r="F96" s="78"/>
-      <c r="G96" s="77"/>
-      <c r="H96" s="78"/>
-      <c r="I96" s="78"/>
-      <c r="J96" s="78"/>
-      <c r="K96" s="78"/>
-      <c r="L96" s="78"/>
-      <c r="M96" s="77"/>
-      <c r="N96" s="79"/>
-      <c r="O96" s="80"/>
-      <c r="P96" s="78"/>
-      <c r="Q96" s="78"/>
-    </row>
-    <row r="97" spans="2:17" ht="23">
+    </row>
+    <row r="97" spans="2:2" ht="23">
       <c r="B97" s="18" t="s">
         <v>554</v>
       </c>
-      <c r="C97" s="77"/>
-      <c r="D97" s="78"/>
-      <c r="E97" s="77"/>
-      <c r="F97" s="78"/>
-      <c r="G97" s="77"/>
-      <c r="H97" s="78"/>
-      <c r="I97" s="78"/>
-      <c r="J97" s="78"/>
-      <c r="K97" s="78"/>
-      <c r="L97" s="78"/>
-      <c r="M97" s="77"/>
-      <c r="N97" s="79"/>
-      <c r="O97" s="80"/>
-      <c r="P97" s="78"/>
-      <c r="Q97" s="78"/>
-    </row>
-    <row r="98" spans="2:17" ht="23">
+    </row>
+    <row r="98" spans="2:2" ht="23">
       <c r="B98" s="18" t="s">
         <v>555</v>
       </c>
-      <c r="C98" s="77"/>
-      <c r="D98" s="78"/>
-      <c r="E98" s="77"/>
-      <c r="F98" s="78"/>
-      <c r="G98" s="77"/>
-      <c r="H98" s="78"/>
-      <c r="I98" s="78"/>
-      <c r="J98" s="78"/>
-      <c r="K98" s="78"/>
-      <c r="L98" s="78"/>
-      <c r="M98" s="77"/>
-      <c r="N98" s="79"/>
-      <c r="O98" s="80"/>
-      <c r="P98" s="78"/>
-      <c r="Q98" s="78"/>
-    </row>
-    <row r="99" spans="2:17" ht="23">
+    </row>
+    <row r="99" spans="2:2" ht="23">
       <c r="B99" s="18" t="s">
         <v>556</v>
       </c>
-      <c r="C99" s="77"/>
-      <c r="D99" s="78"/>
-      <c r="E99" s="77"/>
-      <c r="F99" s="78"/>
-      <c r="G99" s="77"/>
-      <c r="H99" s="78"/>
-      <c r="I99" s="78"/>
-      <c r="J99" s="78"/>
-      <c r="K99" s="78"/>
-      <c r="L99" s="78"/>
-      <c r="M99" s="77"/>
-      <c r="N99" s="79"/>
-      <c r="O99" s="80"/>
-      <c r="P99" s="78"/>
-      <c r="Q99" s="78"/>
-    </row>
-    <row r="100" spans="2:17" ht="23">
+    </row>
+    <row r="100" spans="2:2" ht="23">
       <c r="B100" s="18" t="s">
         <v>557</v>
       </c>
-      <c r="C100" s="77"/>
-      <c r="D100" s="78"/>
-      <c r="E100" s="77"/>
-      <c r="F100" s="78"/>
-      <c r="G100" s="77"/>
-      <c r="H100" s="78"/>
-      <c r="I100" s="78"/>
-      <c r="J100" s="78"/>
-      <c r="K100" s="78"/>
-      <c r="L100" s="78"/>
-      <c r="M100" s="77"/>
-      <c r="N100" s="79"/>
-      <c r="O100" s="80"/>
-      <c r="P100" s="78"/>
-      <c r="Q100" s="78"/>
-    </row>
-    <row r="101" spans="2:17" ht="23">
+    </row>
+    <row r="101" spans="2:2" ht="23">
       <c r="B101" s="18" t="s">
         <v>558</v>
       </c>
-      <c r="C101" s="77"/>
-      <c r="D101" s="78"/>
-      <c r="E101" s="77"/>
-      <c r="F101" s="78"/>
-      <c r="G101" s="77"/>
-      <c r="H101" s="78"/>
-      <c r="I101" s="78"/>
-      <c r="J101" s="78"/>
-      <c r="K101" s="78"/>
-      <c r="L101" s="78"/>
-      <c r="M101" s="77"/>
-      <c r="N101" s="79"/>
-      <c r="O101" s="80"/>
-      <c r="P101" s="78"/>
-      <c r="Q101" s="78"/>
-    </row>
-    <row r="102" spans="2:17" ht="23">
+    </row>
+    <row r="102" spans="2:2" ht="23">
       <c r="B102" s="18" t="s">
         <v>559</v>
       </c>
-      <c r="C102" s="77"/>
-      <c r="D102" s="78"/>
-      <c r="E102" s="77"/>
-      <c r="F102" s="78"/>
-      <c r="G102" s="77"/>
-      <c r="H102" s="78"/>
-      <c r="I102" s="78"/>
-      <c r="J102" s="78"/>
-      <c r="K102" s="78"/>
-      <c r="L102" s="78"/>
-      <c r="M102" s="77"/>
-      <c r="N102" s="79"/>
-      <c r="O102" s="80"/>
-      <c r="P102" s="78"/>
-      <c r="Q102" s="78"/>
-    </row>
-    <row r="103" spans="2:17" ht="23">
+    </row>
+    <row r="103" spans="2:2" ht="23">
       <c r="B103" s="18" t="s">
         <v>560</v>
       </c>
-      <c r="C103" s="77"/>
-      <c r="D103" s="78"/>
-      <c r="E103" s="77"/>
-      <c r="F103" s="78"/>
-      <c r="G103" s="77"/>
-      <c r="H103" s="78"/>
-      <c r="I103" s="78"/>
-      <c r="J103" s="78"/>
-      <c r="K103" s="78"/>
-      <c r="L103" s="78"/>
-      <c r="M103" s="77"/>
-      <c r="N103" s="79"/>
-      <c r="O103" s="80"/>
-      <c r="P103" s="78"/>
-      <c r="Q103" s="78"/>
-    </row>
-    <row r="104" spans="2:17" ht="23">
+    </row>
+    <row r="104" spans="2:2" ht="23">
       <c r="B104" s="18" t="s">
         <v>561</v>
       </c>
-      <c r="C104" s="77"/>
-      <c r="D104" s="78"/>
-      <c r="E104" s="77"/>
-      <c r="F104" s="78"/>
-      <c r="G104" s="77"/>
-      <c r="H104" s="78"/>
-      <c r="I104" s="78"/>
-      <c r="J104" s="78"/>
-      <c r="K104" s="78"/>
-      <c r="L104" s="78"/>
-      <c r="M104" s="77"/>
-      <c r="N104" s="79"/>
-      <c r="O104" s="80"/>
-      <c r="P104" s="78"/>
-      <c r="Q104" s="78"/>
-    </row>
-    <row r="105" spans="2:17" ht="23">
+    </row>
+    <row r="105" spans="2:2" ht="23">
       <c r="B105" s="18" t="s">
         <v>562</v>
       </c>
-      <c r="C105" s="77"/>
-      <c r="D105" s="78"/>
-      <c r="E105" s="77"/>
-      <c r="F105" s="78"/>
-      <c r="G105" s="77"/>
-      <c r="H105" s="78"/>
-      <c r="I105" s="78"/>
-      <c r="J105" s="78"/>
-      <c r="K105" s="78"/>
-      <c r="L105" s="78"/>
-      <c r="M105" s="77"/>
-      <c r="N105" s="79"/>
-      <c r="O105" s="80"/>
-      <c r="P105" s="78"/>
-      <c r="Q105" s="78"/>
-    </row>
-    <row r="106" spans="2:17" ht="23">
+    </row>
+    <row r="106" spans="2:2" ht="23">
       <c r="B106" s="18" t="s">
         <v>563</v>
       </c>
-      <c r="C106" s="77"/>
-      <c r="D106" s="78"/>
-      <c r="E106" s="77"/>
-      <c r="F106" s="78"/>
-      <c r="G106" s="77"/>
-      <c r="H106" s="78"/>
-      <c r="I106" s="78"/>
-      <c r="J106" s="78"/>
-      <c r="K106" s="78"/>
-      <c r="L106" s="78"/>
-      <c r="M106" s="77"/>
-      <c r="N106" s="79"/>
-      <c r="O106" s="80"/>
-      <c r="P106" s="78"/>
-      <c r="Q106" s="78"/>
-    </row>
-    <row r="107" spans="2:17" ht="23">
+    </row>
+    <row r="107" spans="2:2" ht="23">
       <c r="B107" s="18" t="s">
         <v>564</v>
       </c>
-      <c r="C107" s="77"/>
-      <c r="D107" s="78"/>
-      <c r="E107" s="77"/>
-      <c r="F107" s="78"/>
-      <c r="G107" s="77"/>
-      <c r="H107" s="78"/>
-      <c r="I107" s="78"/>
-      <c r="J107" s="78"/>
-      <c r="K107" s="78"/>
-      <c r="L107" s="78"/>
-      <c r="M107" s="77"/>
-      <c r="N107" s="79"/>
-      <c r="O107" s="80"/>
-      <c r="P107" s="78"/>
-      <c r="Q107" s="78"/>
-    </row>
-    <row r="108" spans="2:17" ht="23">
+    </row>
+    <row r="108" spans="2:2" ht="23">
       <c r="B108" s="18" t="s">
         <v>565</v>
       </c>
-      <c r="C108" s="77"/>
-      <c r="D108" s="78"/>
-      <c r="E108" s="77"/>
-      <c r="F108" s="78"/>
-      <c r="G108" s="77"/>
-      <c r="H108" s="78"/>
-      <c r="I108" s="78"/>
-      <c r="J108" s="78"/>
-      <c r="K108" s="78"/>
-      <c r="L108" s="78"/>
-      <c r="M108" s="77"/>
-      <c r="N108" s="79"/>
-      <c r="O108" s="80"/>
-      <c r="P108" s="78"/>
-      <c r="Q108" s="78"/>
-    </row>
-    <row r="109" spans="2:17" ht="23">
+    </row>
+    <row r="109" spans="2:2" ht="23">
       <c r="B109" s="18" t="s">
         <v>566</v>
       </c>
-      <c r="C109" s="77"/>
-      <c r="D109" s="78"/>
-      <c r="E109" s="77"/>
-      <c r="F109" s="78"/>
-      <c r="G109" s="77"/>
-      <c r="H109" s="78"/>
-      <c r="I109" s="78"/>
-      <c r="J109" s="78"/>
-      <c r="K109" s="78"/>
-      <c r="L109" s="78"/>
-      <c r="M109" s="77"/>
-      <c r="N109" s="79"/>
-      <c r="O109" s="80"/>
-      <c r="P109" s="78"/>
-      <c r="Q109" s="78"/>
-    </row>
-    <row r="110" spans="2:17" ht="23">
+    </row>
+    <row r="110" spans="2:2" ht="23">
       <c r="B110" s="18" t="s">
         <v>567</v>
       </c>
-      <c r="C110" s="77"/>
-      <c r="D110" s="78"/>
-      <c r="E110" s="77"/>
-      <c r="F110" s="78"/>
-      <c r="G110" s="77"/>
-      <c r="H110" s="78"/>
-      <c r="I110" s="78"/>
-      <c r="J110" s="78"/>
-      <c r="K110" s="78"/>
-      <c r="L110" s="78"/>
-      <c r="M110" s="77"/>
-      <c r="N110" s="79"/>
-      <c r="O110" s="80"/>
-      <c r="P110" s="78"/>
-      <c r="Q110" s="78"/>
-    </row>
-    <row r="111" spans="2:17" ht="23">
+    </row>
+    <row r="111" spans="2:2" ht="23">
       <c r="B111" s="18" t="s">
         <v>568</v>
       </c>
-      <c r="C111" s="77"/>
-      <c r="D111" s="78"/>
-      <c r="E111" s="77"/>
-      <c r="F111" s="78"/>
-      <c r="G111" s="77"/>
-      <c r="H111" s="78"/>
-      <c r="I111" s="78"/>
-      <c r="J111" s="78"/>
-      <c r="K111" s="78"/>
-      <c r="L111" s="78"/>
-      <c r="M111" s="77"/>
-      <c r="N111" s="79"/>
-      <c r="O111" s="80"/>
-      <c r="P111" s="78"/>
-      <c r="Q111" s="78"/>
-    </row>
-    <row r="112" spans="2:17" ht="23">
+    </row>
+    <row r="112" spans="2:2" ht="23">
       <c r="B112" s="18" t="s">
         <v>569</v>
       </c>
-      <c r="C112" s="77"/>
-      <c r="D112" s="78"/>
-      <c r="E112" s="77"/>
-      <c r="F112" s="78"/>
-      <c r="G112" s="77"/>
-      <c r="H112" s="78"/>
-      <c r="I112" s="78"/>
-      <c r="J112" s="78"/>
-      <c r="K112" s="78"/>
-      <c r="L112" s="78"/>
-      <c r="M112" s="77"/>
-      <c r="N112" s="79"/>
-      <c r="O112" s="80"/>
-      <c r="P112" s="78"/>
-      <c r="Q112" s="78"/>
     </row>
     <row r="113" spans="2:30" ht="23">
-      <c r="B113" s="76" t="s">
+      <c r="B113" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C113" s="77"/>
-      <c r="D113" s="78"/>
-      <c r="E113" s="77"/>
-      <c r="F113" s="78"/>
-      <c r="G113" s="77"/>
-      <c r="H113" s="78"/>
-      <c r="I113" s="78"/>
-      <c r="J113" s="78"/>
-      <c r="K113" s="78"/>
-      <c r="L113" s="78"/>
-      <c r="M113" s="77"/>
-      <c r="N113" s="79"/>
-      <c r="O113" s="80"/>
-      <c r="P113" s="78"/>
-      <c r="Q113" s="78"/>
     </row>
     <row r="114" spans="2:30" ht="23">
-      <c r="B114" s="76" t="s">
+      <c r="B114" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="C114" s="77"/>
-      <c r="D114" s="78"/>
-      <c r="E114" s="77"/>
-      <c r="F114" s="78"/>
-      <c r="G114" s="77"/>
-      <c r="H114" s="78"/>
-      <c r="I114" s="78"/>
-      <c r="J114" s="78"/>
-      <c r="K114" s="78"/>
-      <c r="L114" s="78"/>
-      <c r="M114" s="77"/>
-      <c r="N114" s="79"/>
-      <c r="O114" s="80"/>
-      <c r="P114" s="78"/>
-      <c r="Q114" s="78"/>
-    </row>
-    <row r="115" spans="2:30" s="70" customFormat="1" ht="23">
-      <c r="B115" s="82" t="s">
+    </row>
+    <row r="115" spans="2:30" ht="23">
+      <c r="B115" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C115" s="83"/>
-      <c r="D115" s="84"/>
-      <c r="E115" s="83"/>
-      <c r="F115" s="84"/>
-      <c r="G115" s="83"/>
-      <c r="H115" s="84"/>
-      <c r="I115" s="84"/>
-      <c r="J115" s="84"/>
-      <c r="K115" s="84"/>
-      <c r="L115" s="84"/>
-      <c r="M115" s="83"/>
-      <c r="N115" s="85"/>
-      <c r="O115" s="86"/>
-      <c r="P115" s="84"/>
-      <c r="Q115" s="84"/>
-      <c r="S115" s="73"/>
-      <c r="T115" s="69"/>
-      <c r="U115" s="71"/>
-      <c r="W115" s="74"/>
-      <c r="X115" s="75"/>
-      <c r="AD115" s="72"/>
     </row>
     <row r="116" spans="2:30" ht="23">
       <c r="B116" s="18" t="s">
         <v>570</v>
       </c>
-      <c r="C116" s="77"/>
-      <c r="D116" s="78"/>
-      <c r="E116" s="77"/>
-      <c r="F116" s="78"/>
-      <c r="G116" s="77"/>
-      <c r="H116" s="78"/>
-      <c r="I116" s="78"/>
-      <c r="J116" s="78"/>
-      <c r="K116" s="78"/>
-      <c r="L116" s="78"/>
-      <c r="M116" s="77"/>
-      <c r="N116" s="79"/>
-      <c r="O116" s="80"/>
-      <c r="P116" s="78"/>
-      <c r="Q116" s="78"/>
     </row>
     <row r="117" spans="2:30" ht="23">
       <c r="B117" s="18" t="s">
         <v>571</v>
       </c>
-      <c r="C117" s="77"/>
-      <c r="D117" s="78"/>
-      <c r="E117" s="77"/>
-      <c r="F117" s="78"/>
-      <c r="G117" s="77"/>
-      <c r="H117" s="78"/>
-      <c r="I117" s="78"/>
-      <c r="J117" s="78"/>
-      <c r="K117" s="78"/>
-      <c r="L117" s="78"/>
-      <c r="M117" s="77"/>
-      <c r="N117" s="79"/>
-      <c r="O117" s="80"/>
-      <c r="P117" s="78"/>
-      <c r="Q117" s="78"/>
     </row>
     <row r="118" spans="2:30" s="29" customFormat="1" ht="23">
       <c r="B118" s="18" t="s">
         <v>572</v>
       </c>
-      <c r="C118" s="77"/>
-      <c r="D118" s="78"/>
-      <c r="E118" s="77"/>
-      <c r="F118" s="78"/>
-      <c r="G118" s="77"/>
-      <c r="H118" s="78"/>
-      <c r="I118" s="78"/>
-      <c r="J118" s="78"/>
-      <c r="K118" s="78"/>
-      <c r="L118" s="78"/>
-      <c r="M118" s="77"/>
-      <c r="N118" s="79"/>
-      <c r="O118" s="80"/>
-      <c r="P118" s="78"/>
-      <c r="Q118" s="78"/>
+      <c r="C118" s="21"/>
+      <c r="D118" s="22"/>
+      <c r="E118" s="21"/>
+      <c r="F118" s="22"/>
+      <c r="G118" s="21"/>
+      <c r="H118" s="22"/>
+      <c r="I118" s="22"/>
+      <c r="J118" s="22"/>
+      <c r="K118" s="22"/>
+      <c r="L118" s="22"/>
+      <c r="M118" s="21"/>
+      <c r="N118" s="23"/>
+      <c r="O118"/>
+      <c r="P118" s="22"/>
+      <c r="Q118" s="22"/>
       <c r="S118" s="34"/>
       <c r="T118" s="28"/>
       <c r="U118" s="30"/>
@@ -21902,21 +19985,21 @@
       <c r="B119" s="18" t="s">
         <v>573</v>
       </c>
-      <c r="C119" s="77"/>
-      <c r="D119" s="78"/>
-      <c r="E119" s="77"/>
-      <c r="F119" s="78"/>
-      <c r="G119" s="77"/>
-      <c r="H119" s="78"/>
-      <c r="I119" s="78"/>
-      <c r="J119" s="78"/>
-      <c r="K119" s="78"/>
-      <c r="L119" s="78"/>
-      <c r="M119" s="77"/>
-      <c r="N119" s="79"/>
-      <c r="O119" s="80"/>
-      <c r="P119" s="78"/>
-      <c r="Q119" s="78"/>
+      <c r="C119" s="21"/>
+      <c r="D119" s="22"/>
+      <c r="E119" s="21"/>
+      <c r="F119" s="22"/>
+      <c r="G119" s="21"/>
+      <c r="H119" s="22"/>
+      <c r="I119" s="22"/>
+      <c r="J119" s="22"/>
+      <c r="K119" s="22"/>
+      <c r="L119" s="22"/>
+      <c r="M119" s="21"/>
+      <c r="N119" s="23"/>
+      <c r="O119"/>
+      <c r="P119" s="22"/>
+      <c r="Q119" s="22"/>
       <c r="S119" s="34"/>
       <c r="T119" s="28"/>
       <c r="U119" s="30"/>
@@ -21928,21 +20011,21 @@
       <c r="B120" s="18" t="s">
         <v>574</v>
       </c>
-      <c r="C120" s="77"/>
-      <c r="D120" s="78"/>
-      <c r="E120" s="77"/>
-      <c r="F120" s="78"/>
-      <c r="G120" s="77"/>
-      <c r="H120" s="78"/>
-      <c r="I120" s="78"/>
-      <c r="J120" s="78"/>
-      <c r="K120" s="78"/>
-      <c r="L120" s="78"/>
-      <c r="M120" s="77"/>
-      <c r="N120" s="79"/>
-      <c r="O120" s="80"/>
-      <c r="P120" s="78"/>
-      <c r="Q120" s="78"/>
+      <c r="C120" s="21"/>
+      <c r="D120" s="22"/>
+      <c r="E120" s="21"/>
+      <c r="F120" s="22"/>
+      <c r="G120" s="21"/>
+      <c r="H120" s="22"/>
+      <c r="I120" s="22"/>
+      <c r="J120" s="22"/>
+      <c r="K120" s="22"/>
+      <c r="L120" s="22"/>
+      <c r="M120" s="21"/>
+      <c r="N120" s="23"/>
+      <c r="O120"/>
+      <c r="P120" s="22"/>
+      <c r="Q120" s="22"/>
       <c r="S120" s="34"/>
       <c r="T120" s="28"/>
       <c r="U120" s="30"/>
@@ -21954,1539 +20037,666 @@
       <c r="B121" s="18" t="s">
         <v>575</v>
       </c>
-      <c r="C121" s="77"/>
-      <c r="D121" s="78"/>
-      <c r="E121" s="77"/>
-      <c r="F121" s="78"/>
-      <c r="G121" s="77"/>
-      <c r="H121" s="78"/>
-      <c r="I121" s="78"/>
-      <c r="J121" s="78"/>
-      <c r="K121" s="78"/>
-      <c r="L121" s="78"/>
-      <c r="M121" s="77"/>
-      <c r="N121" s="79"/>
-      <c r="O121" s="80"/>
-      <c r="P121" s="78"/>
-      <c r="Q121" s="78"/>
     </row>
     <row r="122" spans="2:30" ht="23">
       <c r="B122" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="C122" s="77"/>
-      <c r="D122" s="78"/>
-      <c r="E122" s="77"/>
-      <c r="F122" s="78"/>
-      <c r="G122" s="77"/>
-      <c r="H122" s="78"/>
-      <c r="I122" s="78"/>
-      <c r="J122" s="78"/>
-      <c r="K122" s="78"/>
-      <c r="L122" s="78"/>
-      <c r="M122" s="77"/>
-      <c r="N122" s="79"/>
-      <c r="O122" s="80"/>
-      <c r="P122" s="78"/>
-      <c r="Q122" s="78"/>
     </row>
     <row r="123" spans="2:30" ht="23">
       <c r="B123" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="C123" s="77"/>
-      <c r="D123" s="78"/>
-      <c r="E123" s="77"/>
-      <c r="F123" s="78"/>
-      <c r="G123" s="77"/>
-      <c r="H123" s="78"/>
-      <c r="I123" s="78"/>
-      <c r="J123" s="78"/>
-      <c r="K123" s="78"/>
-      <c r="L123" s="78"/>
-      <c r="M123" s="77"/>
-      <c r="N123" s="79"/>
-      <c r="O123" s="80"/>
-      <c r="P123" s="78"/>
-      <c r="Q123" s="78"/>
     </row>
     <row r="124" spans="2:30" ht="23">
       <c r="B124" s="18" t="s">
         <v>578</v>
       </c>
-      <c r="C124" s="77"/>
-      <c r="D124" s="78"/>
-      <c r="E124" s="77"/>
-      <c r="F124" s="78"/>
-      <c r="G124" s="77"/>
-      <c r="H124" s="78"/>
-      <c r="I124" s="78"/>
-      <c r="J124" s="78"/>
-      <c r="K124" s="78"/>
-      <c r="L124" s="78"/>
-      <c r="M124" s="77"/>
-      <c r="N124" s="79"/>
-      <c r="O124" s="80"/>
-      <c r="P124" s="78"/>
-      <c r="Q124" s="78"/>
     </row>
     <row r="125" spans="2:30" ht="23">
       <c r="B125" s="18" t="s">
         <v>579</v>
       </c>
-      <c r="C125" s="77"/>
-      <c r="D125" s="78"/>
-      <c r="E125" s="77"/>
-      <c r="F125" s="78"/>
-      <c r="G125" s="77"/>
-      <c r="H125" s="78"/>
-      <c r="I125" s="78"/>
-      <c r="J125" s="78"/>
-      <c r="K125" s="78"/>
-      <c r="L125" s="78"/>
-      <c r="M125" s="77"/>
-      <c r="N125" s="79"/>
-      <c r="O125" s="80"/>
-      <c r="P125" s="78"/>
-      <c r="Q125" s="78"/>
     </row>
     <row r="126" spans="2:30" ht="23">
       <c r="B126" s="18" t="s">
         <v>580</v>
       </c>
-      <c r="C126" s="77"/>
-      <c r="D126" s="78"/>
-      <c r="E126" s="77"/>
-      <c r="F126" s="78"/>
-      <c r="G126" s="77"/>
-      <c r="H126" s="78"/>
-      <c r="I126" s="78"/>
-      <c r="J126" s="78"/>
-      <c r="K126" s="78"/>
-      <c r="L126" s="78"/>
-      <c r="M126" s="77"/>
-      <c r="N126" s="79"/>
-      <c r="O126" s="80"/>
-      <c r="P126" s="78"/>
-      <c r="Q126" s="78"/>
     </row>
     <row r="127" spans="2:30" ht="23">
       <c r="B127" s="18" t="s">
         <v>581</v>
       </c>
-      <c r="C127" s="77"/>
-      <c r="D127" s="78"/>
-      <c r="E127" s="77"/>
-      <c r="F127" s="78"/>
-      <c r="G127" s="77"/>
-      <c r="H127" s="78"/>
-      <c r="I127" s="78"/>
-      <c r="J127" s="78"/>
-      <c r="K127" s="78"/>
-      <c r="L127" s="78"/>
-      <c r="M127" s="77"/>
-      <c r="N127" s="79"/>
-      <c r="O127" s="80"/>
-      <c r="P127" s="78"/>
-      <c r="Q127" s="78"/>
     </row>
     <row r="128" spans="2:30" ht="23">
       <c r="B128" s="18" t="s">
         <v>582</v>
       </c>
-      <c r="C128" s="77"/>
-      <c r="D128" s="78"/>
-      <c r="E128" s="77"/>
-      <c r="F128" s="78"/>
-      <c r="G128" s="77"/>
-      <c r="H128" s="78"/>
-      <c r="I128" s="78"/>
-      <c r="J128" s="78"/>
-      <c r="K128" s="78"/>
-      <c r="L128" s="78"/>
-      <c r="M128" s="77"/>
-      <c r="N128" s="79"/>
-      <c r="O128" s="80"/>
-      <c r="P128" s="78"/>
-      <c r="Q128" s="78"/>
-    </row>
-    <row r="129" spans="2:17" ht="23">
+    </row>
+    <row r="129" spans="2:2" ht="23">
       <c r="B129" s="18" t="s">
         <v>583</v>
       </c>
-      <c r="C129" s="77"/>
-      <c r="D129" s="78"/>
-      <c r="E129" s="77"/>
-      <c r="F129" s="78"/>
-      <c r="G129" s="77"/>
-      <c r="H129" s="78"/>
-      <c r="I129" s="78"/>
-      <c r="J129" s="78"/>
-      <c r="K129" s="78"/>
-      <c r="L129" s="78"/>
-      <c r="M129" s="77"/>
-      <c r="N129" s="79"/>
-      <c r="O129" s="80"/>
-      <c r="P129" s="78"/>
-      <c r="Q129" s="78"/>
-    </row>
-    <row r="130" spans="2:17" ht="23">
+    </row>
+    <row r="130" spans="2:2" ht="23">
       <c r="B130" s="18" t="s">
         <v>584</v>
       </c>
-      <c r="C130" s="77"/>
-      <c r="D130" s="78"/>
-      <c r="E130" s="77"/>
-      <c r="F130" s="78"/>
-      <c r="G130" s="77"/>
-      <c r="H130" s="78"/>
-      <c r="I130" s="78"/>
-      <c r="J130" s="78"/>
-      <c r="K130" s="78"/>
-      <c r="L130" s="78"/>
-      <c r="M130" s="77"/>
-      <c r="N130" s="79"/>
-      <c r="O130" s="80"/>
-      <c r="P130" s="78"/>
-      <c r="Q130" s="78"/>
-    </row>
-    <row r="131" spans="2:17" ht="23">
+    </row>
+    <row r="131" spans="2:2" ht="23">
       <c r="B131" s="18" t="s">
         <v>585</v>
       </c>
-      <c r="C131" s="77"/>
-      <c r="D131" s="78"/>
-      <c r="E131" s="77"/>
-      <c r="F131" s="78"/>
-      <c r="G131" s="77"/>
-      <c r="H131" s="78"/>
-      <c r="I131" s="78"/>
-      <c r="J131" s="78"/>
-      <c r="K131" s="78"/>
-      <c r="L131" s="78"/>
-      <c r="M131" s="77"/>
-      <c r="N131" s="79"/>
-      <c r="O131" s="80"/>
-      <c r="P131" s="78"/>
-      <c r="Q131" s="78"/>
-    </row>
-    <row r="132" spans="2:17" ht="23">
+    </row>
+    <row r="132" spans="2:2" ht="23">
       <c r="B132" s="18" t="s">
         <v>586</v>
       </c>
-      <c r="C132" s="77"/>
-      <c r="D132" s="78"/>
-      <c r="E132" s="77"/>
-      <c r="F132" s="78"/>
-      <c r="G132" s="77"/>
-      <c r="H132" s="78"/>
-      <c r="I132" s="78"/>
-      <c r="J132" s="78"/>
-      <c r="K132" s="78"/>
-      <c r="L132" s="78"/>
-      <c r="M132" s="77"/>
-      <c r="N132" s="79"/>
-      <c r="O132" s="80"/>
-      <c r="P132" s="78"/>
-      <c r="Q132" s="78"/>
-    </row>
-    <row r="133" spans="2:17" ht="23">
+    </row>
+    <row r="133" spans="2:2" ht="23">
       <c r="B133" s="18" t="s">
         <v>587</v>
       </c>
-      <c r="C133" s="77"/>
-      <c r="D133" s="78"/>
-      <c r="E133" s="77"/>
-      <c r="F133" s="78"/>
-      <c r="G133" s="77"/>
-      <c r="H133" s="78"/>
-      <c r="I133" s="78"/>
-      <c r="J133" s="78"/>
-      <c r="K133" s="78"/>
-      <c r="L133" s="78"/>
-      <c r="M133" s="77"/>
-      <c r="N133" s="79"/>
-      <c r="O133" s="80"/>
-      <c r="P133" s="78"/>
-      <c r="Q133" s="78"/>
-    </row>
-    <row r="134" spans="2:17" ht="23">
+    </row>
+    <row r="134" spans="2:2" ht="23">
       <c r="B134" s="18" t="s">
         <v>588</v>
       </c>
-      <c r="C134" s="77"/>
-      <c r="D134" s="78"/>
-      <c r="E134" s="77"/>
-      <c r="F134" s="78"/>
-      <c r="G134" s="77"/>
-      <c r="H134" s="78"/>
-      <c r="I134" s="78"/>
-      <c r="J134" s="78"/>
-      <c r="K134" s="78"/>
-      <c r="L134" s="78"/>
-      <c r="M134" s="77"/>
-      <c r="N134" s="79"/>
-      <c r="O134" s="80"/>
-      <c r="P134" s="78"/>
-      <c r="Q134" s="78"/>
-    </row>
-    <row r="135" spans="2:17" ht="23">
+    </row>
+    <row r="135" spans="2:2" ht="23">
       <c r="B135" s="18" t="s">
         <v>589</v>
       </c>
-      <c r="C135" s="77"/>
-      <c r="D135" s="78"/>
-      <c r="E135" s="77"/>
-      <c r="F135" s="78"/>
-      <c r="G135" s="77"/>
-      <c r="H135" s="78"/>
-      <c r="I135" s="78"/>
-      <c r="J135" s="78"/>
-      <c r="K135" s="78"/>
-      <c r="L135" s="78"/>
-      <c r="M135" s="77"/>
-      <c r="N135" s="79"/>
-      <c r="O135" s="80"/>
-      <c r="P135" s="78"/>
-      <c r="Q135" s="78"/>
-    </row>
-    <row r="136" spans="2:17" ht="23">
+    </row>
+    <row r="136" spans="2:2" ht="23">
       <c r="B136" s="18" t="s">
         <v>590</v>
       </c>
-      <c r="C136" s="77"/>
-      <c r="D136" s="78"/>
-      <c r="E136" s="77"/>
-      <c r="F136" s="78"/>
-      <c r="G136" s="77"/>
-      <c r="H136" s="78"/>
-      <c r="I136" s="78"/>
-      <c r="J136" s="78"/>
-      <c r="K136" s="78"/>
-      <c r="L136" s="78"/>
-      <c r="M136" s="77"/>
-      <c r="N136" s="79"/>
-      <c r="O136" s="80"/>
-      <c r="P136" s="78"/>
-      <c r="Q136" s="78"/>
-    </row>
-    <row r="137" spans="2:17" ht="23">
+    </row>
+    <row r="137" spans="2:2" ht="23">
       <c r="B137" s="18" t="s">
         <v>591</v>
       </c>
-      <c r="C137" s="77"/>
-      <c r="D137" s="78"/>
-      <c r="E137" s="77"/>
-      <c r="F137" s="78"/>
-      <c r="G137" s="77"/>
-      <c r="H137" s="78"/>
-      <c r="I137" s="78"/>
-      <c r="J137" s="78"/>
-      <c r="K137" s="78"/>
-      <c r="L137" s="78"/>
-      <c r="M137" s="77"/>
-      <c r="N137" s="79"/>
-      <c r="O137" s="80"/>
-      <c r="P137" s="78"/>
-      <c r="Q137" s="78"/>
-    </row>
-    <row r="138" spans="2:17" ht="23">
+    </row>
+    <row r="138" spans="2:2" ht="23">
       <c r="B138" s="18" t="s">
         <v>592</v>
       </c>
-      <c r="C138" s="77"/>
-      <c r="D138" s="78"/>
-      <c r="E138" s="77"/>
-      <c r="F138" s="78"/>
-      <c r="G138" s="77"/>
-      <c r="H138" s="78"/>
-      <c r="I138" s="78"/>
-      <c r="J138" s="78"/>
-      <c r="K138" s="78"/>
-      <c r="L138" s="78"/>
-      <c r="M138" s="77"/>
-      <c r="N138" s="79"/>
-      <c r="O138" s="80"/>
-      <c r="P138" s="78"/>
-      <c r="Q138" s="78"/>
-    </row>
-    <row r="139" spans="2:17" ht="23">
+    </row>
+    <row r="139" spans="2:2" ht="23">
       <c r="B139" s="18" t="s">
         <v>593</v>
       </c>
-      <c r="C139" s="77"/>
-      <c r="D139" s="78"/>
-      <c r="E139" s="77"/>
-      <c r="F139" s="78"/>
-      <c r="G139" s="77"/>
-      <c r="H139" s="78"/>
-      <c r="I139" s="78"/>
-      <c r="J139" s="78"/>
-      <c r="K139" s="78"/>
-      <c r="L139" s="78"/>
-      <c r="M139" s="77"/>
-      <c r="N139" s="79"/>
-      <c r="O139" s="80"/>
-      <c r="P139" s="78"/>
-      <c r="Q139" s="78"/>
-    </row>
-    <row r="140" spans="2:17" ht="23">
+    </row>
+    <row r="140" spans="2:2" ht="23">
       <c r="B140" s="18" t="s">
         <v>594</v>
       </c>
-      <c r="C140" s="77"/>
-      <c r="D140" s="78"/>
-      <c r="E140" s="77"/>
-      <c r="F140" s="78"/>
-      <c r="G140" s="77"/>
-      <c r="H140" s="78"/>
-      <c r="I140" s="78"/>
-      <c r="J140" s="78"/>
-      <c r="K140" s="78"/>
-      <c r="L140" s="78"/>
-      <c r="M140" s="77"/>
-      <c r="N140" s="79"/>
-      <c r="O140" s="80"/>
-      <c r="P140" s="78"/>
-      <c r="Q140" s="78"/>
-    </row>
-    <row r="141" spans="2:17" ht="23">
+    </row>
+    <row r="141" spans="2:2" ht="23">
       <c r="B141" s="18" t="s">
         <v>595</v>
       </c>
-      <c r="C141" s="77"/>
-      <c r="D141" s="78"/>
-      <c r="E141" s="77"/>
-      <c r="F141" s="78"/>
-      <c r="G141" s="77"/>
-      <c r="H141" s="78"/>
-      <c r="I141" s="78"/>
-      <c r="J141" s="78"/>
-      <c r="K141" s="78"/>
-      <c r="L141" s="78"/>
-      <c r="M141" s="77"/>
-      <c r="N141" s="79"/>
-      <c r="O141" s="80"/>
-      <c r="P141" s="78"/>
-      <c r="Q141" s="78"/>
-    </row>
-    <row r="142" spans="2:17" ht="23">
+    </row>
+    <row r="142" spans="2:2" ht="23">
       <c r="B142" s="18" t="s">
         <v>596</v>
       </c>
-      <c r="C142" s="77"/>
-      <c r="D142" s="78"/>
-      <c r="E142" s="77"/>
-      <c r="F142" s="78"/>
-      <c r="G142" s="77"/>
-      <c r="H142" s="78"/>
-      <c r="I142" s="78"/>
-      <c r="J142" s="78"/>
-      <c r="K142" s="78"/>
-      <c r="L142" s="78"/>
-      <c r="M142" s="77"/>
-      <c r="N142" s="79"/>
-      <c r="O142" s="80"/>
-      <c r="P142" s="78"/>
-      <c r="Q142" s="78"/>
-    </row>
-    <row r="143" spans="2:17" ht="23">
+    </row>
+    <row r="143" spans="2:2" ht="23">
       <c r="B143" s="18" t="s">
         <v>597</v>
       </c>
-      <c r="C143" s="77"/>
-      <c r="D143" s="78"/>
-      <c r="E143" s="77"/>
-      <c r="F143" s="78"/>
-      <c r="G143" s="77"/>
-      <c r="H143" s="78"/>
-      <c r="I143" s="78"/>
-      <c r="J143" s="78"/>
-      <c r="K143" s="78"/>
-      <c r="L143" s="78"/>
-      <c r="M143" s="77"/>
-      <c r="N143" s="79"/>
-      <c r="O143" s="80"/>
-      <c r="P143" s="78"/>
-      <c r="Q143" s="78"/>
-    </row>
-    <row r="144" spans="2:17" ht="23">
+    </row>
+    <row r="144" spans="2:2" ht="23">
       <c r="B144" s="18" t="s">
         <v>598</v>
       </c>
-      <c r="C144" s="77"/>
-      <c r="D144" s="78"/>
-      <c r="E144" s="77"/>
-      <c r="F144" s="78"/>
-      <c r="G144" s="77"/>
-      <c r="H144" s="78"/>
-      <c r="I144" s="78"/>
-      <c r="J144" s="78"/>
-      <c r="K144" s="78"/>
-      <c r="L144" s="78"/>
-      <c r="M144" s="77"/>
-      <c r="N144" s="79"/>
-      <c r="O144" s="80"/>
-      <c r="P144" s="78"/>
-      <c r="Q144" s="78"/>
-    </row>
-    <row r="145" spans="2:17" ht="23">
+    </row>
+    <row r="145" spans="2:2" ht="23">
       <c r="B145" s="18" t="s">
         <v>599</v>
       </c>
-      <c r="C145" s="77"/>
-      <c r="D145" s="78"/>
-      <c r="E145" s="77"/>
-      <c r="F145" s="78"/>
-      <c r="G145" s="77"/>
-      <c r="H145" s="78"/>
-      <c r="I145" s="78"/>
-      <c r="J145" s="78"/>
-      <c r="K145" s="78"/>
-      <c r="L145" s="78"/>
-      <c r="M145" s="77"/>
-      <c r="N145" s="79"/>
-      <c r="O145" s="80"/>
-      <c r="P145" s="78"/>
-      <c r="Q145" s="78"/>
-    </row>
-    <row r="146" spans="2:17" ht="23">
+    </row>
+    <row r="146" spans="2:2" ht="23">
       <c r="B146" s="18" t="s">
         <v>600</v>
       </c>
-      <c r="C146" s="77"/>
-      <c r="D146" s="78"/>
-      <c r="E146" s="77"/>
-      <c r="F146" s="78"/>
-      <c r="G146" s="77"/>
-      <c r="H146" s="78"/>
-      <c r="I146" s="78"/>
-      <c r="J146" s="78"/>
-      <c r="K146" s="78"/>
-      <c r="L146" s="78"/>
-      <c r="M146" s="77"/>
-      <c r="N146" s="79"/>
-      <c r="O146" s="80"/>
-      <c r="P146" s="78"/>
-      <c r="Q146" s="78"/>
-    </row>
-    <row r="147" spans="2:17" ht="23">
+    </row>
+    <row r="147" spans="2:2" ht="23">
       <c r="B147" s="18" t="s">
         <v>601</v>
       </c>
-      <c r="C147" s="77"/>
-      <c r="D147" s="78"/>
-      <c r="E147" s="77"/>
-      <c r="F147" s="78"/>
-      <c r="G147" s="77"/>
-      <c r="H147" s="78"/>
-      <c r="I147" s="78"/>
-      <c r="J147" s="78"/>
-      <c r="K147" s="78"/>
-      <c r="L147" s="78"/>
-      <c r="M147" s="77"/>
-      <c r="N147" s="79"/>
-      <c r="O147" s="80"/>
-      <c r="P147" s="78"/>
-      <c r="Q147" s="78"/>
-    </row>
-    <row r="148" spans="2:17" ht="23">
+    </row>
+    <row r="148" spans="2:2" ht="23">
       <c r="B148" s="18" t="s">
         <v>602</v>
       </c>
-      <c r="C148" s="77"/>
-      <c r="D148" s="78"/>
-      <c r="E148" s="77"/>
-      <c r="F148" s="78"/>
-      <c r="G148" s="77"/>
-      <c r="H148" s="78"/>
-      <c r="I148" s="78"/>
-      <c r="J148" s="78"/>
-      <c r="K148" s="78"/>
-      <c r="L148" s="78"/>
-      <c r="M148" s="77"/>
-      <c r="N148" s="79"/>
-      <c r="O148" s="80"/>
-      <c r="P148" s="78"/>
-      <c r="Q148" s="78"/>
-    </row>
-    <row r="149" spans="2:17" ht="23">
+    </row>
+    <row r="149" spans="2:2" ht="23">
       <c r="B149" s="18" t="s">
         <v>603</v>
       </c>
-      <c r="C149" s="77"/>
-      <c r="D149" s="78"/>
-      <c r="E149" s="77"/>
-      <c r="F149" s="78"/>
-      <c r="G149" s="77"/>
-      <c r="H149" s="78"/>
-      <c r="I149" s="78"/>
-      <c r="J149" s="78"/>
-      <c r="K149" s="78"/>
-      <c r="L149" s="78"/>
-      <c r="M149" s="77"/>
-      <c r="N149" s="79"/>
-      <c r="O149" s="80"/>
-      <c r="P149" s="78"/>
-      <c r="Q149" s="78"/>
-    </row>
-    <row r="150" spans="2:17" ht="23">
+    </row>
+    <row r="150" spans="2:2" ht="23">
       <c r="B150" s="18" t="s">
         <v>604</v>
       </c>
-      <c r="C150" s="77"/>
-      <c r="D150" s="78"/>
-      <c r="E150" s="77"/>
-      <c r="F150" s="78"/>
-      <c r="G150" s="77"/>
-      <c r="H150" s="78"/>
-      <c r="I150" s="78"/>
-      <c r="J150" s="78"/>
-      <c r="K150" s="78"/>
-      <c r="L150" s="78"/>
-      <c r="M150" s="77"/>
-      <c r="N150" s="79"/>
-      <c r="O150" s="80"/>
-      <c r="P150" s="78"/>
-      <c r="Q150" s="78"/>
-    </row>
-    <row r="151" spans="2:17" ht="23">
+    </row>
+    <row r="151" spans="2:2" ht="23">
       <c r="B151" s="18" t="s">
         <v>605</v>
       </c>
-      <c r="C151" s="77"/>
-      <c r="D151" s="78"/>
-      <c r="E151" s="77"/>
-      <c r="F151" s="78"/>
-      <c r="G151" s="77"/>
-      <c r="H151" s="78"/>
-      <c r="I151" s="78"/>
-      <c r="J151" s="78"/>
-      <c r="K151" s="78"/>
-      <c r="L151" s="78"/>
-      <c r="M151" s="77"/>
-      <c r="N151" s="79"/>
-      <c r="O151" s="80"/>
-      <c r="P151" s="78"/>
-      <c r="Q151" s="78"/>
-    </row>
-    <row r="152" spans="2:17" ht="23">
+    </row>
+    <row r="152" spans="2:2" ht="23">
       <c r="B152" s="18" t="s">
         <v>606</v>
       </c>
-      <c r="C152" s="77"/>
-      <c r="D152" s="78"/>
-      <c r="E152" s="77"/>
-      <c r="F152" s="78"/>
-      <c r="G152" s="77"/>
-      <c r="H152" s="78"/>
-      <c r="I152" s="78"/>
-      <c r="J152" s="78"/>
-      <c r="K152" s="78"/>
-      <c r="L152" s="78"/>
-      <c r="M152" s="77"/>
-      <c r="N152" s="79"/>
-      <c r="O152" s="80"/>
-      <c r="P152" s="78"/>
-      <c r="Q152" s="78"/>
-    </row>
-    <row r="153" spans="2:17" ht="23">
+    </row>
+    <row r="153" spans="2:2" ht="23">
       <c r="B153" s="18" t="s">
         <v>607</v>
       </c>
-      <c r="C153" s="77"/>
-      <c r="D153" s="78"/>
-      <c r="E153" s="77"/>
-      <c r="F153" s="78"/>
-      <c r="G153" s="77"/>
-      <c r="H153" s="78"/>
-      <c r="I153" s="78"/>
-      <c r="J153" s="78"/>
-      <c r="K153" s="78"/>
-      <c r="L153" s="78"/>
-      <c r="M153" s="77"/>
-      <c r="N153" s="79"/>
-      <c r="O153" s="80"/>
-      <c r="P153" s="78"/>
-      <c r="Q153" s="78"/>
-    </row>
-    <row r="154" spans="2:17" ht="23">
+    </row>
+    <row r="154" spans="2:2" ht="23">
       <c r="B154" s="18" t="s">
         <v>608</v>
       </c>
-      <c r="C154" s="77"/>
-      <c r="D154" s="78"/>
-      <c r="E154" s="77"/>
-      <c r="F154" s="78"/>
-      <c r="G154" s="77"/>
-      <c r="H154" s="78"/>
-      <c r="I154" s="78"/>
-      <c r="J154" s="78"/>
-      <c r="K154" s="78"/>
-      <c r="L154" s="78"/>
-      <c r="M154" s="77"/>
-      <c r="N154" s="79"/>
-      <c r="O154" s="80"/>
-      <c r="P154" s="78"/>
-      <c r="Q154" s="78"/>
-    </row>
-    <row r="155" spans="2:17" ht="23">
+    </row>
+    <row r="155" spans="2:2" ht="23">
       <c r="B155" s="18" t="s">
         <v>609</v>
       </c>
-      <c r="C155" s="77"/>
-      <c r="D155" s="78"/>
-      <c r="E155" s="77"/>
-      <c r="F155" s="78"/>
-      <c r="G155" s="77"/>
-      <c r="H155" s="78"/>
-      <c r="I155" s="78"/>
-      <c r="J155" s="78"/>
-      <c r="K155" s="78"/>
-      <c r="L155" s="78"/>
-      <c r="M155" s="77"/>
-      <c r="N155" s="79"/>
-      <c r="O155" s="80"/>
-      <c r="P155" s="78"/>
-      <c r="Q155" s="78"/>
-    </row>
-    <row r="156" spans="2:17" ht="23">
+    </row>
+    <row r="156" spans="2:2" ht="23">
       <c r="B156" s="18" t="s">
         <v>610</v>
       </c>
-      <c r="C156" s="77"/>
-      <c r="D156" s="78"/>
-      <c r="E156" s="77"/>
-      <c r="F156" s="78"/>
-      <c r="G156" s="77"/>
-      <c r="H156" s="78"/>
-      <c r="I156" s="78"/>
-      <c r="J156" s="78"/>
-      <c r="K156" s="78"/>
-      <c r="L156" s="78"/>
-      <c r="M156" s="77"/>
-      <c r="N156" s="79"/>
-      <c r="O156" s="80"/>
-      <c r="P156" s="78"/>
-      <c r="Q156" s="78"/>
-    </row>
-    <row r="157" spans="2:17" ht="23">
+    </row>
+    <row r="157" spans="2:2" ht="23">
       <c r="B157" s="18" t="s">
         <v>611</v>
       </c>
-      <c r="C157" s="77"/>
-      <c r="D157" s="78"/>
-      <c r="E157" s="77"/>
-      <c r="F157" s="78"/>
-      <c r="G157" s="77"/>
-      <c r="H157" s="78"/>
-      <c r="I157" s="78"/>
-      <c r="J157" s="78"/>
-      <c r="K157" s="78"/>
-      <c r="L157" s="78"/>
-      <c r="M157" s="77"/>
-      <c r="N157" s="79"/>
-      <c r="O157" s="80"/>
-      <c r="P157" s="78"/>
-      <c r="Q157" s="78"/>
-    </row>
-    <row r="158" spans="2:17" ht="23">
+    </row>
+    <row r="158" spans="2:2" ht="23">
       <c r="B158" s="18" t="s">
         <v>612</v>
       </c>
-      <c r="C158" s="77"/>
-      <c r="D158" s="78"/>
-      <c r="E158" s="77"/>
-      <c r="F158" s="78"/>
-      <c r="G158" s="77"/>
-      <c r="H158" s="78"/>
-      <c r="I158" s="78"/>
-      <c r="J158" s="78"/>
-      <c r="K158" s="78"/>
-      <c r="L158" s="78"/>
-      <c r="M158" s="77"/>
-      <c r="N158" s="79"/>
-      <c r="O158" s="80"/>
-      <c r="P158" s="78"/>
-      <c r="Q158" s="78"/>
-    </row>
-    <row r="159" spans="2:17" ht="23">
+    </row>
+    <row r="159" spans="2:2" ht="23">
       <c r="B159" s="18" t="s">
         <v>613</v>
       </c>
-      <c r="C159" s="77"/>
-      <c r="D159" s="78"/>
-      <c r="E159" s="77"/>
-      <c r="F159" s="78"/>
-      <c r="G159" s="77"/>
-      <c r="H159" s="78"/>
-      <c r="I159" s="78"/>
-      <c r="J159" s="78"/>
-      <c r="K159" s="78"/>
-      <c r="L159" s="78"/>
-      <c r="M159" s="77"/>
-      <c r="N159" s="79"/>
-      <c r="O159" s="80"/>
-      <c r="P159" s="78"/>
-      <c r="Q159" s="78"/>
-    </row>
-    <row r="160" spans="2:17" ht="23">
+    </row>
+    <row r="160" spans="2:2" ht="23">
       <c r="B160" s="18" t="s">
         <v>614</v>
       </c>
-      <c r="C160" s="77"/>
-      <c r="D160" s="78"/>
-      <c r="E160" s="77"/>
-      <c r="F160" s="78"/>
-      <c r="G160" s="77"/>
-      <c r="H160" s="78"/>
-      <c r="I160" s="78"/>
-      <c r="J160" s="78"/>
-      <c r="K160" s="78"/>
-      <c r="L160" s="78"/>
-      <c r="M160" s="77"/>
-      <c r="N160" s="79"/>
-      <c r="O160" s="80"/>
-      <c r="P160" s="78"/>
-      <c r="Q160" s="78"/>
-    </row>
-    <row r="161" spans="2:17" ht="23">
+    </row>
+    <row r="161" spans="2:2" ht="23">
       <c r="B161" s="18" t="s">
         <v>615</v>
       </c>
-      <c r="C161" s="77"/>
-      <c r="D161" s="78"/>
-      <c r="E161" s="77"/>
-      <c r="F161" s="78"/>
-      <c r="G161" s="77"/>
-      <c r="H161" s="78"/>
-      <c r="I161" s="78"/>
-      <c r="J161" s="78"/>
-      <c r="K161" s="78"/>
-      <c r="L161" s="78"/>
-      <c r="M161" s="77"/>
-      <c r="N161" s="79"/>
-      <c r="O161" s="80"/>
-      <c r="P161" s="78"/>
-      <c r="Q161" s="78"/>
-    </row>
-    <row r="162" spans="2:17" ht="23">
+    </row>
+    <row r="162" spans="2:2" ht="23">
       <c r="B162" s="18" t="s">
         <v>616</v>
       </c>
-      <c r="C162" s="77"/>
-      <c r="D162" s="78"/>
-      <c r="E162" s="77"/>
-      <c r="F162" s="78"/>
-      <c r="G162" s="77"/>
-      <c r="H162" s="78"/>
-      <c r="I162" s="78"/>
-      <c r="J162" s="78"/>
-      <c r="K162" s="78"/>
-      <c r="L162" s="78"/>
-      <c r="M162" s="77"/>
-      <c r="N162" s="79"/>
-      <c r="O162" s="80"/>
-      <c r="P162" s="78"/>
-      <c r="Q162" s="78"/>
-    </row>
-    <row r="163" spans="2:17" ht="23">
+    </row>
+    <row r="163" spans="2:2" ht="23">
       <c r="B163" s="18" t="s">
         <v>617</v>
       </c>
-      <c r="C163" s="77"/>
-      <c r="D163" s="78"/>
-      <c r="E163" s="77"/>
-      <c r="F163" s="78"/>
-      <c r="G163" s="77"/>
-      <c r="H163" s="78"/>
-      <c r="I163" s="78"/>
-      <c r="J163" s="78"/>
-      <c r="K163" s="78"/>
-      <c r="L163" s="78"/>
-      <c r="M163" s="77"/>
-      <c r="N163" s="79"/>
-      <c r="O163" s="80"/>
-      <c r="P163" s="78"/>
-      <c r="Q163" s="78"/>
-    </row>
-    <row r="164" spans="2:17" ht="23">
+    </row>
+    <row r="164" spans="2:2" ht="23">
       <c r="B164" s="18" t="s">
         <v>618</v>
       </c>
-      <c r="C164" s="77"/>
-      <c r="D164" s="78"/>
-      <c r="E164" s="77"/>
-      <c r="F164" s="78"/>
-      <c r="G164" s="77"/>
-      <c r="H164" s="78"/>
-      <c r="I164" s="78"/>
-      <c r="J164" s="78"/>
-      <c r="K164" s="78"/>
-      <c r="L164" s="78"/>
-      <c r="M164" s="77"/>
-      <c r="N164" s="79"/>
-      <c r="O164" s="80"/>
-      <c r="P164" s="78"/>
-      <c r="Q164" s="78"/>
-    </row>
-    <row r="165" spans="2:17" ht="23">
+    </row>
+    <row r="165" spans="2:2" ht="23">
       <c r="B165" s="18" t="s">
         <v>619</v>
       </c>
-      <c r="C165" s="77"/>
-      <c r="D165" s="78"/>
-      <c r="E165" s="77"/>
-      <c r="F165" s="78"/>
-      <c r="G165" s="77"/>
-      <c r="H165" s="78"/>
-      <c r="I165" s="78"/>
-      <c r="J165" s="78"/>
-      <c r="K165" s="78"/>
-      <c r="L165" s="78"/>
-      <c r="M165" s="77"/>
-      <c r="N165" s="79"/>
-      <c r="O165" s="80"/>
-      <c r="P165" s="78"/>
-      <c r="Q165" s="78"/>
-    </row>
-    <row r="166" spans="2:17" ht="23">
+    </row>
+    <row r="166" spans="2:2" ht="23">
       <c r="B166" s="18" t="s">
         <v>620</v>
       </c>
-      <c r="C166" s="77"/>
-      <c r="D166" s="78"/>
-      <c r="E166" s="77"/>
-      <c r="F166" s="78"/>
-      <c r="G166" s="77"/>
-      <c r="H166" s="78"/>
-      <c r="I166" s="78"/>
-      <c r="J166" s="78"/>
-      <c r="K166" s="78"/>
-      <c r="L166" s="78"/>
-      <c r="M166" s="77"/>
-      <c r="N166" s="79"/>
-      <c r="O166" s="80"/>
-      <c r="P166" s="78"/>
-      <c r="Q166" s="78"/>
-    </row>
-    <row r="167" spans="2:17" ht="23">
+    </row>
+    <row r="167" spans="2:2" ht="23">
       <c r="B167" s="18" t="s">
         <v>621</v>
       </c>
-      <c r="C167" s="77"/>
-      <c r="D167" s="78"/>
-      <c r="E167" s="77"/>
-      <c r="F167" s="78"/>
-      <c r="G167" s="77"/>
-      <c r="H167" s="78"/>
-      <c r="I167" s="78"/>
-      <c r="J167" s="78"/>
-      <c r="K167" s="78"/>
-      <c r="L167" s="78"/>
-      <c r="M167" s="77"/>
-      <c r="N167" s="79"/>
-      <c r="O167" s="80"/>
-      <c r="P167" s="78"/>
-      <c r="Q167" s="78"/>
-    </row>
-    <row r="168" spans="2:17" ht="23">
+    </row>
+    <row r="168" spans="2:2" ht="23">
       <c r="B168" s="18" t="s">
         <v>622</v>
       </c>
-      <c r="C168" s="77"/>
-      <c r="D168" s="78"/>
-      <c r="E168" s="77"/>
-      <c r="F168" s="78"/>
-      <c r="G168" s="77"/>
-      <c r="H168" s="78"/>
-      <c r="I168" s="78"/>
-      <c r="J168" s="78"/>
-      <c r="K168" s="78"/>
-      <c r="L168" s="78"/>
-      <c r="M168" s="77"/>
-      <c r="N168" s="79"/>
-      <c r="O168" s="80"/>
-      <c r="P168" s="78"/>
-      <c r="Q168" s="78"/>
-    </row>
-    <row r="169" spans="2:17" ht="23">
+    </row>
+    <row r="169" spans="2:2" ht="23">
       <c r="B169" s="18" t="s">
         <v>623</v>
       </c>
-      <c r="C169" s="77"/>
-      <c r="D169" s="78"/>
-      <c r="E169" s="77"/>
-      <c r="F169" s="78"/>
-      <c r="G169" s="77"/>
-      <c r="H169" s="78"/>
-      <c r="I169" s="78"/>
-      <c r="J169" s="78"/>
-      <c r="K169" s="78"/>
-      <c r="L169" s="78"/>
-      <c r="M169" s="77"/>
-      <c r="N169" s="79"/>
-      <c r="O169" s="80"/>
-      <c r="P169" s="78"/>
-      <c r="Q169" s="78"/>
-    </row>
-    <row r="170" spans="2:17" ht="23">
+    </row>
+    <row r="170" spans="2:2" ht="23">
       <c r="B170" s="18" t="s">
         <v>624</v>
       </c>
-      <c r="C170" s="77"/>
-      <c r="D170" s="78"/>
-      <c r="E170" s="77"/>
-      <c r="F170" s="78"/>
-      <c r="G170" s="77"/>
-      <c r="H170" s="78"/>
-      <c r="I170" s="78"/>
-      <c r="J170" s="78"/>
-      <c r="K170" s="78"/>
-      <c r="L170" s="78"/>
-      <c r="M170" s="77"/>
-      <c r="N170" s="79"/>
-      <c r="O170" s="80"/>
-      <c r="P170" s="78"/>
-      <c r="Q170" s="78"/>
-    </row>
-    <row r="171" spans="2:17" ht="23">
+    </row>
+    <row r="171" spans="2:2" ht="23">
       <c r="B171" s="18" t="s">
         <v>625</v>
       </c>
-      <c r="C171" s="77"/>
-      <c r="D171" s="78"/>
-      <c r="E171" s="77"/>
-      <c r="F171" s="78"/>
-      <c r="G171" s="77"/>
-      <c r="H171" s="78"/>
-      <c r="I171" s="78"/>
-      <c r="J171" s="78"/>
-      <c r="K171" s="78"/>
-      <c r="L171" s="78"/>
-      <c r="M171" s="77"/>
-      <c r="N171" s="79"/>
-      <c r="O171" s="80"/>
-      <c r="P171" s="78"/>
-      <c r="Q171" s="78"/>
-    </row>
-    <row r="172" spans="2:17" ht="23">
+    </row>
+    <row r="172" spans="2:2" ht="23">
       <c r="B172" s="18" t="s">
         <v>626</v>
       </c>
-      <c r="C172" s="77"/>
-      <c r="D172" s="78"/>
-      <c r="E172" s="77"/>
-      <c r="F172" s="78"/>
-      <c r="G172" s="77"/>
-      <c r="H172" s="78"/>
-      <c r="I172" s="78"/>
-      <c r="J172" s="78"/>
-      <c r="K172" s="78"/>
-      <c r="L172" s="78"/>
-      <c r="M172" s="77"/>
-      <c r="N172" s="79"/>
-      <c r="O172" s="80"/>
-      <c r="P172" s="78"/>
-      <c r="Q172" s="78"/>
-    </row>
-    <row r="173" spans="2:17" ht="23">
+    </row>
+    <row r="173" spans="2:2" ht="23">
       <c r="B173" s="18" t="s">
         <v>627</v>
       </c>
-      <c r="C173" s="77"/>
-      <c r="D173" s="78"/>
-      <c r="E173" s="77"/>
-      <c r="F173" s="78"/>
-      <c r="G173" s="77"/>
-      <c r="H173" s="78"/>
-      <c r="I173" s="78"/>
-      <c r="J173" s="78"/>
-      <c r="K173" s="78"/>
-      <c r="L173" s="78"/>
-      <c r="M173" s="77"/>
-      <c r="N173" s="79"/>
-      <c r="O173" s="80"/>
-      <c r="P173" s="78"/>
-      <c r="Q173" s="78"/>
-    </row>
-    <row r="174" spans="2:17" ht="23">
+    </row>
+    <row r="174" spans="2:2" ht="23">
       <c r="B174" s="18" t="s">
         <v>628</v>
       </c>
-      <c r="C174" s="77"/>
-      <c r="D174" s="78"/>
-      <c r="E174" s="77"/>
-      <c r="F174" s="78"/>
-      <c r="G174" s="77"/>
-      <c r="H174" s="78"/>
-      <c r="I174" s="78"/>
-      <c r="J174" s="78"/>
-      <c r="K174" s="78"/>
-      <c r="L174" s="78"/>
-      <c r="M174" s="77"/>
-      <c r="N174" s="79"/>
-      <c r="O174" s="80"/>
-      <c r="P174" s="78"/>
-      <c r="Q174" s="78"/>
-    </row>
-    <row r="175" spans="2:17" ht="23">
+    </row>
+    <row r="175" spans="2:2" ht="23">
       <c r="B175" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="C175" s="77"/>
-      <c r="D175" s="78"/>
-      <c r="E175" s="77"/>
-      <c r="F175" s="78"/>
-      <c r="G175" s="77"/>
-      <c r="H175" s="78"/>
-      <c r="I175" s="78"/>
-      <c r="J175" s="78"/>
-      <c r="K175" s="78"/>
-      <c r="L175" s="78"/>
-      <c r="M175" s="77"/>
-      <c r="N175" s="79"/>
-      <c r="O175" s="80"/>
-      <c r="P175" s="78"/>
-      <c r="Q175" s="78"/>
-    </row>
-    <row r="176" spans="2:17" ht="23">
+    </row>
+    <row r="176" spans="2:2" ht="23">
       <c r="B176" s="18" t="s">
         <v>630</v>
       </c>
-      <c r="C176" s="77"/>
-      <c r="D176" s="78"/>
-      <c r="E176" s="77"/>
-      <c r="F176" s="78"/>
-      <c r="G176" s="77"/>
-      <c r="H176" s="78"/>
-      <c r="I176" s="78"/>
-      <c r="J176" s="78"/>
-      <c r="K176" s="78"/>
-      <c r="L176" s="78"/>
-      <c r="M176" s="77"/>
-      <c r="N176" s="79"/>
-      <c r="O176" s="80"/>
-      <c r="P176" s="78"/>
-      <c r="Q176" s="78"/>
-    </row>
-    <row r="177" spans="2:17" ht="23">
+    </row>
+    <row r="177" spans="2:2" ht="23">
       <c r="B177" s="18" t="s">
         <v>631</v>
       </c>
-      <c r="C177" s="77"/>
-      <c r="D177" s="78"/>
-      <c r="E177" s="77"/>
-      <c r="F177" s="78"/>
-      <c r="G177" s="77"/>
-      <c r="H177" s="78"/>
-      <c r="I177" s="78"/>
-      <c r="J177" s="78"/>
-      <c r="K177" s="78"/>
-      <c r="L177" s="78"/>
-      <c r="M177" s="77"/>
-      <c r="N177" s="79"/>
-      <c r="O177" s="80"/>
-      <c r="P177" s="78"/>
-      <c r="Q177" s="78"/>
-    </row>
-    <row r="178" spans="2:17" ht="23">
+    </row>
+    <row r="178" spans="2:2" ht="23">
       <c r="B178" s="18" t="s">
         <v>632</v>
       </c>
-      <c r="C178" s="77"/>
-      <c r="D178" s="78"/>
-      <c r="E178" s="77"/>
-      <c r="F178" s="78"/>
-      <c r="G178" s="77"/>
-      <c r="H178" s="78"/>
-      <c r="I178" s="78"/>
-      <c r="J178" s="78"/>
-      <c r="K178" s="78"/>
-      <c r="L178" s="78"/>
-      <c r="M178" s="77"/>
-      <c r="N178" s="79"/>
-      <c r="O178" s="80"/>
-      <c r="P178" s="78"/>
-      <c r="Q178" s="78"/>
-    </row>
-    <row r="179" spans="2:17" ht="23">
+    </row>
+    <row r="179" spans="2:2" ht="23">
       <c r="B179" s="18" t="s">
         <v>633</v>
       </c>
-      <c r="C179" s="77"/>
-      <c r="D179" s="78"/>
-      <c r="E179" s="77"/>
-      <c r="F179" s="78"/>
-      <c r="G179" s="77"/>
-      <c r="H179" s="78"/>
-      <c r="I179" s="78"/>
-      <c r="J179" s="78"/>
-      <c r="K179" s="78"/>
-      <c r="L179" s="78"/>
-      <c r="M179" s="77"/>
-      <c r="N179" s="79"/>
-      <c r="O179" s="80"/>
-      <c r="P179" s="78"/>
-      <c r="Q179" s="78"/>
-    </row>
-    <row r="180" spans="2:17" ht="23">
+    </row>
+    <row r="180" spans="2:2" ht="23">
       <c r="B180" s="18" t="s">
         <v>634</v>
       </c>
-      <c r="C180" s="77"/>
-      <c r="D180" s="78"/>
-      <c r="E180" s="77"/>
-      <c r="F180" s="78"/>
-      <c r="G180" s="77"/>
-      <c r="H180" s="78"/>
-      <c r="I180" s="78"/>
-      <c r="J180" s="78"/>
-      <c r="K180" s="78"/>
-      <c r="L180" s="78"/>
-      <c r="M180" s="77"/>
-      <c r="N180" s="79"/>
-      <c r="O180" s="80"/>
-      <c r="P180" s="78"/>
-      <c r="Q180" s="78"/>
-    </row>
-    <row r="181" spans="2:17" ht="23">
+    </row>
+    <row r="181" spans="2:2" ht="23">
       <c r="B181" s="18" t="s">
         <v>635</v>
       </c>
-      <c r="C181" s="77"/>
-      <c r="D181" s="78"/>
-      <c r="E181" s="77"/>
-      <c r="F181" s="78"/>
-      <c r="G181" s="77"/>
-      <c r="H181" s="78"/>
-      <c r="I181" s="78"/>
-      <c r="J181" s="78"/>
-      <c r="K181" s="78"/>
-      <c r="L181" s="78"/>
-      <c r="M181" s="77"/>
-      <c r="N181" s="79"/>
-      <c r="O181" s="80"/>
-      <c r="P181" s="78"/>
-      <c r="Q181" s="78"/>
-    </row>
-    <row r="182" spans="2:17" ht="23">
+    </row>
+    <row r="182" spans="2:2" ht="23">
       <c r="B182" s="18" t="s">
         <v>636</v>
       </c>
-      <c r="C182" s="77"/>
-      <c r="D182" s="78"/>
-      <c r="E182" s="77"/>
-      <c r="F182" s="78"/>
-      <c r="G182" s="77"/>
-      <c r="H182" s="78"/>
-      <c r="I182" s="78"/>
-      <c r="J182" s="78"/>
-      <c r="K182" s="78"/>
-      <c r="L182" s="78"/>
-      <c r="M182" s="77"/>
-      <c r="N182" s="79"/>
-      <c r="O182" s="80"/>
-      <c r="P182" s="78"/>
-      <c r="Q182" s="78"/>
-    </row>
-    <row r="183" spans="2:17" ht="23">
+    </row>
+    <row r="183" spans="2:2" ht="23">
       <c r="B183" s="18" t="s">
         <v>637</v>
       </c>
-      <c r="C183" s="77"/>
-      <c r="D183" s="78"/>
-      <c r="E183" s="77"/>
-      <c r="F183" s="78"/>
-      <c r="G183" s="77"/>
-      <c r="H183" s="78"/>
-      <c r="I183" s="78"/>
-      <c r="J183" s="78"/>
-      <c r="K183" s="78"/>
-      <c r="L183" s="78"/>
-      <c r="M183" s="77"/>
-      <c r="N183" s="79"/>
-      <c r="O183" s="80"/>
-      <c r="P183" s="78"/>
-      <c r="Q183" s="78"/>
-    </row>
-    <row r="184" spans="2:17" ht="23">
+    </row>
+    <row r="184" spans="2:2" ht="23">
       <c r="B184" s="18" t="s">
         <v>638</v>
       </c>
-      <c r="C184" s="77"/>
-      <c r="D184" s="78"/>
-      <c r="E184" s="77"/>
-      <c r="F184" s="78"/>
-      <c r="G184" s="77"/>
-      <c r="H184" s="78"/>
-      <c r="I184" s="78"/>
-      <c r="J184" s="78"/>
-      <c r="K184" s="78"/>
-      <c r="L184" s="78"/>
-      <c r="M184" s="77"/>
-      <c r="N184" s="79"/>
-      <c r="O184" s="80"/>
-      <c r="P184" s="78"/>
-      <c r="Q184" s="78"/>
-    </row>
-    <row r="185" spans="2:17" ht="23">
+    </row>
+    <row r="185" spans="2:2" ht="23">
       <c r="B185" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C185" s="77"/>
-      <c r="D185" s="78"/>
-      <c r="E185" s="77"/>
-      <c r="F185" s="78"/>
-      <c r="G185" s="77"/>
-      <c r="H185" s="78"/>
-      <c r="I185" s="78"/>
-      <c r="J185" s="78"/>
-      <c r="K185" s="78"/>
-      <c r="L185" s="78"/>
-      <c r="M185" s="77"/>
-      <c r="N185" s="79"/>
-      <c r="O185" s="80"/>
-      <c r="P185" s="78"/>
-      <c r="Q185" s="78"/>
-    </row>
-    <row r="186" spans="2:17" ht="23">
+    </row>
+    <row r="186" spans="2:2" ht="23">
       <c r="B186" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="C186" s="77"/>
-      <c r="D186" s="78"/>
-      <c r="E186" s="77"/>
-      <c r="F186" s="78"/>
-      <c r="G186" s="77"/>
-      <c r="H186" s="78"/>
-      <c r="I186" s="78"/>
-      <c r="J186" s="78"/>
-      <c r="K186" s="78"/>
-      <c r="L186" s="78"/>
-      <c r="M186" s="77"/>
-      <c r="N186" s="79"/>
-      <c r="O186" s="80"/>
-      <c r="P186" s="78"/>
-      <c r="Q186" s="78"/>
-    </row>
-    <row r="187" spans="2:17" ht="23">
+    </row>
+    <row r="187" spans="2:2" ht="23">
       <c r="B187" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="C187" s="77"/>
-      <c r="D187" s="78"/>
-      <c r="E187" s="77"/>
-      <c r="F187" s="78"/>
-      <c r="G187" s="77"/>
-      <c r="H187" s="78"/>
-      <c r="I187" s="78"/>
-      <c r="J187" s="78"/>
-      <c r="K187" s="78"/>
-      <c r="L187" s="78"/>
-      <c r="M187" s="77"/>
-      <c r="N187" s="79"/>
-      <c r="O187" s="80"/>
-      <c r="P187" s="78"/>
-      <c r="Q187" s="78"/>
-    </row>
-    <row r="188" spans="2:17" ht="23">
+    </row>
+    <row r="188" spans="2:2" ht="23">
       <c r="B188" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="C188" s="77"/>
-      <c r="D188" s="78"/>
-      <c r="E188" s="77"/>
-      <c r="F188" s="78"/>
-      <c r="G188" s="77"/>
-      <c r="H188" s="78"/>
-      <c r="I188" s="78"/>
-      <c r="J188" s="78"/>
-      <c r="K188" s="78"/>
-      <c r="L188" s="78"/>
-      <c r="M188" s="77"/>
-      <c r="N188" s="79"/>
-      <c r="O188" s="80"/>
-      <c r="P188" s="78"/>
-      <c r="Q188" s="78"/>
-    </row>
-    <row r="189" spans="2:17" ht="23">
+    </row>
+    <row r="189" spans="2:2" ht="23">
       <c r="B189" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="C189" s="77"/>
-      <c r="D189" s="78"/>
-      <c r="E189" s="77"/>
-      <c r="F189" s="78"/>
-      <c r="G189" s="77"/>
-      <c r="H189" s="78"/>
-      <c r="I189" s="78"/>
-      <c r="J189" s="78"/>
-      <c r="K189" s="78"/>
-      <c r="L189" s="78"/>
-      <c r="M189" s="77"/>
-      <c r="N189" s="79"/>
-      <c r="O189" s="80"/>
-      <c r="P189" s="78"/>
-      <c r="Q189" s="78"/>
-    </row>
-    <row r="190" spans="2:17" ht="23">
+    </row>
+    <row r="190" spans="2:2" ht="23">
       <c r="B190" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="C190" s="77"/>
-      <c r="D190" s="78"/>
-      <c r="E190" s="77"/>
-      <c r="F190" s="78"/>
-      <c r="G190" s="77"/>
-      <c r="H190" s="78"/>
-      <c r="I190" s="78"/>
-      <c r="J190" s="78"/>
-      <c r="K190" s="78"/>
-      <c r="L190" s="78"/>
-      <c r="M190" s="77"/>
-      <c r="N190" s="79"/>
-      <c r="O190" s="80"/>
-      <c r="P190" s="78"/>
-      <c r="Q190" s="78"/>
-    </row>
-    <row r="191" spans="2:17" ht="23">
+    </row>
+    <row r="191" spans="2:2" ht="23">
       <c r="B191" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C191" s="77"/>
-      <c r="D191" s="78"/>
-      <c r="E191" s="77"/>
-      <c r="F191" s="78"/>
-      <c r="G191" s="77"/>
-      <c r="H191" s="78"/>
-      <c r="I191" s="78"/>
-      <c r="J191" s="78"/>
-      <c r="K191" s="78"/>
-      <c r="L191" s="78"/>
-      <c r="M191" s="77"/>
-      <c r="N191" s="79"/>
-      <c r="O191" s="80"/>
-      <c r="P191" s="78"/>
-      <c r="Q191" s="78"/>
-    </row>
-    <row r="192" spans="2:17" ht="23">
+    </row>
+    <row r="192" spans="2:2" ht="23">
       <c r="B192" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="C192" s="77"/>
-      <c r="D192" s="78"/>
-      <c r="E192" s="77"/>
-      <c r="F192" s="78"/>
-      <c r="G192" s="77"/>
-      <c r="H192" s="78"/>
-      <c r="I192" s="78"/>
-      <c r="J192" s="78"/>
-      <c r="K192" s="78"/>
-      <c r="L192" s="78"/>
-      <c r="M192" s="77"/>
-      <c r="N192" s="79"/>
-      <c r="O192" s="80"/>
-      <c r="P192" s="78"/>
-      <c r="Q192" s="78"/>
-    </row>
-    <row r="193" spans="2:17" ht="23">
+    </row>
+    <row r="193" spans="2:2" ht="23">
       <c r="B193" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="C193" s="77"/>
-      <c r="D193" s="78"/>
-      <c r="E193" s="77"/>
-      <c r="F193" s="78"/>
-      <c r="G193" s="77"/>
-      <c r="H193" s="78"/>
-      <c r="I193" s="78"/>
-      <c r="J193" s="78"/>
-      <c r="K193" s="78"/>
-      <c r="L193" s="78"/>
-      <c r="M193" s="77"/>
-      <c r="N193" s="79"/>
-      <c r="O193" s="80"/>
-      <c r="P193" s="78"/>
-      <c r="Q193" s="78"/>
-    </row>
-    <row r="194" spans="2:17" ht="23">
+    </row>
+    <row r="194" spans="2:2" ht="23">
       <c r="B194" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="C194" s="77"/>
-      <c r="D194" s="78"/>
-      <c r="E194" s="77"/>
-      <c r="F194" s="78"/>
-      <c r="G194" s="77"/>
-      <c r="H194" s="78"/>
-      <c r="I194" s="78"/>
-      <c r="J194" s="78"/>
-      <c r="K194" s="78"/>
-      <c r="L194" s="78"/>
-      <c r="M194" s="77"/>
-      <c r="N194" s="79"/>
-      <c r="O194" s="80"/>
-      <c r="P194" s="78"/>
-      <c r="Q194" s="78"/>
-    </row>
-    <row r="195" spans="2:17" ht="23">
+    </row>
+    <row r="195" spans="2:2" ht="23">
       <c r="B195" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="C195" s="77"/>
-      <c r="D195" s="78"/>
-      <c r="E195" s="77"/>
-      <c r="F195" s="78"/>
-      <c r="G195" s="77"/>
-      <c r="H195" s="78"/>
-      <c r="I195" s="78"/>
-      <c r="J195" s="78"/>
-      <c r="K195" s="78"/>
-      <c r="L195" s="78"/>
-      <c r="M195" s="77"/>
-      <c r="N195" s="79"/>
-      <c r="O195" s="80"/>
-      <c r="P195" s="78"/>
-      <c r="Q195" s="78"/>
-    </row>
-    <row r="196" spans="2:17" ht="23">
+    </row>
+    <row r="196" spans="2:2" ht="23">
       <c r="B196" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="C196" s="77"/>
-      <c r="D196" s="78"/>
-      <c r="E196" s="77"/>
-      <c r="F196" s="78"/>
-      <c r="G196" s="77"/>
-      <c r="H196" s="78"/>
-      <c r="I196" s="78"/>
-      <c r="J196" s="78"/>
-      <c r="K196" s="78"/>
-      <c r="L196" s="78"/>
-      <c r="M196" s="77"/>
-      <c r="N196" s="79"/>
-      <c r="O196" s="80"/>
-      <c r="P196" s="78"/>
-      <c r="Q196" s="78"/>
-    </row>
-    <row r="197" spans="2:17">
-      <c r="B197" s="78"/>
-      <c r="C197" s="77"/>
-      <c r="D197" s="78"/>
-      <c r="E197" s="77"/>
-      <c r="F197" s="78"/>
-      <c r="G197" s="77"/>
-      <c r="H197" s="78"/>
-      <c r="I197" s="78"/>
-      <c r="J197" s="78"/>
-      <c r="K197" s="78"/>
-      <c r="L197" s="78"/>
-      <c r="M197" s="77"/>
-      <c r="N197" s="79"/>
-      <c r="O197" s="80"/>
-      <c r="P197" s="78"/>
-      <c r="Q197" s="78"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6C26D0D-500B-AA41-9E70-BC6C65DEE3CD}">
+  <dimension ref="B3:B152"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="23"/>
+  <cols>
+    <col min="2" max="2" width="89.625" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:2">
+      <c r="B3" s="48" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="45" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="44" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="45" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="48" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="44" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="46" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" s="46" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" s="46" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="45" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="48" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="44" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="46" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="46" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="46" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="45" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="48" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="44" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="46" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="46" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="45" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="48" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="44" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="46" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="46" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="45" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="48" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="47" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="48" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="43" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="49" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="44" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="46" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="46" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="46" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="45" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="48" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="44" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="46" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="48" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="44" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="46" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="45" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="48" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="43" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="1"/>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="1"/>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106" s="1"/>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116" s="1"/>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129" s="1"/>
+    </row>
+    <row r="139" spans="2:2">
+      <c r="B139" s="1"/>
+    </row>
+    <row r="152" spans="2:2">
+      <c r="B152" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
